--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>136422902</v>
       </c>
       <c r="B49" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136422929</v>
       </c>
       <c r="B50" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136422936</v>
       </c>
       <c r="B51" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>135387419</v>
       </c>
       <c r="B232" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>136050490</v>
       </c>
       <c r="B257" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>135991610</v>
       </c>
       <c r="B307" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>129134736</v>
       </c>
       <c r="B391" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>136422902</v>
       </c>
       <c r="B49" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136422929</v>
       </c>
       <c r="B50" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136422936</v>
       </c>
       <c r="B51" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>135827391</v>
       </c>
       <c r="B65" t="n">
-        <v>56943</v>
+        <v>56956</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>135970465</v>
       </c>
       <c r="B165" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>135387419</v>
       </c>
       <c r="B232" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27255,7 +27255,7 @@
         <v>135970367</v>
       </c>
       <c r="B247" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>136050518</v>
       </c>
       <c r="B255" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>136050490</v>
       </c>
       <c r="B257" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>135970485</v>
       </c>
       <c r="B294" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>135991610</v>
       </c>
       <c r="B307" t="n">
-        <v>93382</v>
+        <v>93395</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>136050600</v>
       </c>
       <c r="B352" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>129134736</v>
       </c>
       <c r="B391" t="n">
-        <v>93404</v>
+        <v>93417</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>136422902</v>
       </c>
       <c r="B49" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>136422929</v>
       </c>
       <c r="B50" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>136422936</v>
       </c>
       <c r="B51" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>135387419</v>
       </c>
       <c r="B232" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>136050490</v>
       </c>
       <c r="B257" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>135991610</v>
       </c>
       <c r="B307" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -43206,7 +43206,7 @@
         <v>129134736</v>
       </c>
       <c r="B391" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>136422902</v>
       </c>
       <c r="B51" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>136422929</v>
       </c>
       <c r="B52" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>136422936</v>
       </c>
       <c r="B53" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>136050490</v>
       </c>
       <c r="B259" t="n">
-        <v>106486</v>
+        <v>106487</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>136801543</v>
       </c>
       <c r="B34" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>136824069</v>
       </c>
       <c r="B35" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>136697189</v>
       </c>
       <c r="B46" t="n">
-        <v>90857</v>
+        <v>90859</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>136422902</v>
       </c>
       <c r="B54" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>136422929</v>
       </c>
       <c r="B55" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>136422936</v>
       </c>
       <c r="B56" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>136823635</v>
       </c>
       <c r="B86" t="n">
-        <v>90857</v>
+        <v>90859</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>136823659</v>
       </c>
       <c r="B87" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>136824686</v>
       </c>
       <c r="B88" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>136823526</v>
       </c>
       <c r="B92" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>136823927</v>
       </c>
       <c r="B105" t="n">
-        <v>90857</v>
+        <v>90859</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>136824654</v>
       </c>
       <c r="B107" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>136823841</v>
       </c>
       <c r="B118" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>136823870</v>
       </c>
       <c r="B119" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>136823898</v>
       </c>
       <c r="B120" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>136823966</v>
       </c>
       <c r="B121" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>136823975</v>
       </c>
       <c r="B122" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>136824666</v>
       </c>
       <c r="B123" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>136823791</v>
       </c>
       <c r="B144" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>136823881</v>
       </c>
       <c r="B145" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>136824642</v>
       </c>
       <c r="B146" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16378,7 +16378,7 @@
         <v>136824678</v>
       </c>
       <c r="B147" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -3623,48 +3623,51 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136842795</v>
+        <v>129624959</v>
       </c>
       <c r="B29" t="n">
-        <v>79477</v>
+        <v>90946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>889</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>687543</v>
+        <v>687752</v>
       </c>
       <c r="R29" t="n">
-        <v>6563558</v>
+        <v>6563242</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3688,22 +3691,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3719,24 +3712,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136842795</t>
+          <t>https://artportalen.se/Sighting/129624959</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129624959</v>
+        <v>129625082</v>
       </c>
       <c r="B30" t="n">
         <v>90946</v>
@@ -3774,10 +3767,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>687752</v>
+        <v>687769</v>
       </c>
       <c r="R30" t="n">
-        <v>6563242</v>
+        <v>6563249</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3836,38 +3829,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624959</t>
+          <t>https://artportalen.se/Sighting/129625082</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129625082</v>
+        <v>128968158</v>
       </c>
       <c r="B31" t="n">
-        <v>90946</v>
+        <v>90659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>889</v>
+        <v>1593</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3876,14 +3869,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>687769</v>
+        <v>687853</v>
       </c>
       <c r="R31" t="n">
-        <v>6563249</v>
+        <v>6563245</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3910,12 +3903,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,38 +3935,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129625082</t>
+          <t>https://artportalen.se/Sighting/128968158</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128968158</v>
+        <v>128398178</v>
       </c>
       <c r="B32" t="n">
-        <v>90659</v>
+        <v>93197</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1593</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3982,14 +3975,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>687853</v>
+        <v>687745</v>
       </c>
       <c r="R32" t="n">
-        <v>6563245</v>
+        <v>6563263</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4016,12 +4009,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4048,16 +4041,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128968158</t>
+          <t>https://artportalen.se/Sighting/128398178</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128398178</v>
+        <v>136801543</v>
       </c>
       <c r="B33" t="n">
-        <v>93197</v>
+        <v>93411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>687745</v>
+        <v>687724</v>
       </c>
       <c r="R33" t="n">
-        <v>6563263</v>
+        <v>6563250</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4122,12 +4115,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4154,16 +4147,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398178</t>
+          <t>https://artportalen.se/Sighting/136801543</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136801543</v>
+        <v>136824069</v>
       </c>
       <c r="B34" t="n">
-        <v>93411</v>
+        <v>93449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4171,21 +4164,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4194,14 +4187,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>687724</v>
+        <v>687851</v>
       </c>
       <c r="R34" t="n">
-        <v>6563250</v>
+        <v>6563233</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4228,12 +4221,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4260,57 +4253,62 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136801543</t>
+          <t>https://artportalen.se/Sighting/136824069</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136824069</v>
+        <v>129624864</v>
       </c>
       <c r="B35" t="n">
-        <v>93449</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>687851</v>
+        <v>687770</v>
       </c>
       <c r="R35" t="n">
-        <v>6563233</v>
+        <v>6563203</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4334,12 +4332,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4348,7 +4346,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4366,16 +4363,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824069</t>
+          <t>https://artportalen.se/Sighting/129624864</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129624864</v>
+        <v>133768363</v>
       </c>
       <c r="B36" t="n">
-        <v>57950</v>
+        <v>56915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4383,16 +4380,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100088</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4405,6 +4402,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -4415,13 +4413,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>687770</v>
+        <v>687789</v>
       </c>
       <c r="R36" t="n">
-        <v>6563203</v>
+        <v>6563204</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4445,12 +4443,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4459,6 +4457,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4476,49 +4475,48 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624864</t>
+          <t>https://artportalen.se/Sighting/133768363</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133768363</v>
+        <v>136697165</v>
       </c>
       <c r="B37" t="n">
-        <v>56915</v>
+        <v>58169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100088</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4526,10 +4524,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>687789</v>
+        <v>687805</v>
       </c>
       <c r="R37" t="n">
-        <v>6563204</v>
+        <v>6563178</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4556,12 +4554,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4570,7 +4568,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4588,16 +4585,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133768363</t>
+          <t>https://artportalen.se/Sighting/136697165</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136697165</v>
+        <v>129592510</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>90946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4605,31 +4602,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>889</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4637,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>687805</v>
+        <v>687663</v>
       </c>
       <c r="R38" t="n">
-        <v>6563178</v>
+        <v>6563403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4667,12 +4659,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På en medelkraftig tall för att vara på hällmark, dock inte så hög.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4681,6 +4678,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4698,13 +4696,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697165</t>
+          <t>https://artportalen.se/Sighting/129592510</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129592510</v>
+        <v>129592546</v>
       </c>
       <c r="B39" t="n">
         <v>90946</v>
@@ -4745,7 +4743,7 @@
         <v>687663</v>
       </c>
       <c r="R39" t="n">
-        <v>6563403</v>
+        <v>6563407</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4782,7 +4780,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På en medelkraftig tall för att vara på hällmark, dock inte så hög.</t>
+          <t>På en mycket klen tall med en diameter på ca 10 cm.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4809,13 +4807,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129592510</t>
+          <t>https://artportalen.se/Sighting/129592546</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129592546</v>
+        <v>129626517</v>
       </c>
       <c r="B40" t="n">
         <v>90946</v>
@@ -4853,10 +4851,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>687663</v>
+        <v>687631</v>
       </c>
       <c r="R40" t="n">
-        <v>6563407</v>
+        <v>6563371</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4883,17 +4881,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På en mycket klen tall med en diameter på ca 10 cm.</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4920,38 +4913,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129592546</t>
+          <t>https://artportalen.se/Sighting/129626517</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129626517</v>
+        <v>112319637</v>
       </c>
       <c r="B41" t="n">
-        <v>90946</v>
+        <v>90659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>889</v>
+        <v>1593</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4960,14 +4953,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>687631</v>
+        <v>687861</v>
       </c>
       <c r="R41" t="n">
-        <v>6563371</v>
+        <v>6563432</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4994,12 +4987,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5026,13 +5019,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129626517</t>
+          <t>https://artportalen.se/Sighting/112319637</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112319637</v>
+        <v>128647001</v>
       </c>
       <c r="B42" t="n">
         <v>90659</v>
@@ -5066,14 +5059,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Vargklova Mosse, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>687861</v>
+        <v>687855</v>
       </c>
       <c r="R42" t="n">
-        <v>6563432</v>
+        <v>6563491</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5100,12 +5093,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5132,13 +5125,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319637</t>
+          <t>https://artportalen.se/Sighting/128647001</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128647001</v>
+        <v>128968206</v>
       </c>
       <c r="B43" t="n">
         <v>90659</v>
@@ -5176,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>687855</v>
+        <v>687633</v>
       </c>
       <c r="R43" t="n">
-        <v>6563491</v>
+        <v>6563411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5206,12 +5199,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5238,16 +5231,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128647001</t>
+          <t>https://artportalen.se/Sighting/128968206</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128968206</v>
+        <v>128887003</v>
       </c>
       <c r="B44" t="n">
-        <v>90659</v>
+        <v>90674</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5255,21 +5248,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5278,14 +5271,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>687633</v>
+        <v>687714</v>
       </c>
       <c r="R44" t="n">
-        <v>6563411</v>
+        <v>6563288</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5312,12 +5305,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5344,16 +5337,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128968206</t>
+          <t>https://artportalen.se/Sighting/128887003</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128887003</v>
+        <v>136697189</v>
       </c>
       <c r="B45" t="n">
-        <v>90674</v>
+        <v>90859</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5378,8 +5371,16 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5388,10 +5389,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>687714</v>
+        <v>687710</v>
       </c>
       <c r="R45" t="n">
-        <v>6563288</v>
+        <v>6563282</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,12 +5419,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2025, då ett ex.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5450,16 +5456,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128887003</t>
+          <t>https://artportalen.se/Sighting/136697189</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136697189</v>
+        <v>112319589</v>
       </c>
       <c r="B46" t="n">
-        <v>90859</v>
+        <v>93213</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5467,45 +5473,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1596</v>
+        <v>2059</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova Mosse, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>687710</v>
+        <v>687874</v>
       </c>
       <c r="R46" t="n">
-        <v>6563282</v>
+        <v>6563521</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5532,17 +5530,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Återfynd, tidigare rapporterad 2025, då ett ex.</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5569,38 +5562,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136697189</t>
+          <t>https://artportalen.se/Sighting/112319589</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112319589</v>
+        <v>112319624</v>
       </c>
       <c r="B47" t="n">
-        <v>93213</v>
+        <v>93189</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5613,10 +5606,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>687874</v>
+        <v>687826</v>
       </c>
       <c r="R47" t="n">
-        <v>6563521</v>
+        <v>6563469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5675,13 +5668,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319589</t>
+          <t>https://artportalen.se/Sighting/112319624</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112319624</v>
+        <v>112319794</v>
       </c>
       <c r="B48" t="n">
         <v>93189</v>
@@ -5715,14 +5708,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Vargklova Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687826</v>
+        <v>687883</v>
       </c>
       <c r="R48" t="n">
-        <v>6563469</v>
+        <v>6563355</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5781,13 +5774,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319624</t>
+          <t>https://artportalen.se/Sighting/112319794</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112319794</v>
+        <v>128646956</v>
       </c>
       <c r="B49" t="n">
         <v>93189</v>
@@ -5821,14 +5814,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>687883</v>
+        <v>687820</v>
       </c>
       <c r="R49" t="n">
-        <v>6563355</v>
+        <v>6563470</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5855,12 +5848,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5887,16 +5880,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112319794</t>
+          <t>https://artportalen.se/Sighting/128646956</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128646956</v>
+        <v>128315320</v>
       </c>
       <c r="B50" t="n">
-        <v>93189</v>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5904,21 +5897,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5927,14 +5920,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>687820</v>
+        <v>687850</v>
       </c>
       <c r="R50" t="n">
-        <v>6563470</v>
+        <v>6563290</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5961,12 +5954,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5993,13 +5986,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646956</t>
+          <t>https://artportalen.se/Sighting/128315320</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128315320</v>
+        <v>128398188</v>
       </c>
       <c r="B51" t="n">
         <v>93197</v>
@@ -6037,10 +6030,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>687850</v>
+        <v>687749</v>
       </c>
       <c r="R51" t="n">
-        <v>6563290</v>
+        <v>6563286</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6067,12 +6060,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6099,13 +6092,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128315320</t>
+          <t>https://artportalen.se/Sighting/128398188</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128398188</v>
+        <v>129192837</v>
       </c>
       <c r="B52" t="n">
         <v>93197</v>
@@ -6139,14 +6132,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>687749</v>
+        <v>687668</v>
       </c>
       <c r="R52" t="n">
-        <v>6563286</v>
+        <v>6563440</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6173,12 +6166,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6205,16 +6198,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128398188</t>
+          <t>https://artportalen.se/Sighting/129192837</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129192837</v>
+        <v>136422902</v>
       </c>
       <c r="B53" t="n">
-        <v>93197</v>
+        <v>93411</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6249,10 +6242,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687668</v>
+        <v>687744</v>
       </c>
       <c r="R53" t="n">
-        <v>6563440</v>
+        <v>6563378</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6279,12 +6272,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6311,13 +6304,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129192837</t>
+          <t>https://artportalen.se/Sighting/136422902</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136422902</v>
+        <v>136422929</v>
       </c>
       <c r="B54" t="n">
         <v>93411</v>
@@ -6355,10 +6348,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687744</v>
+        <v>687677</v>
       </c>
       <c r="R54" t="n">
-        <v>6563378</v>
+        <v>6563484</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6417,13 +6410,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422902</t>
+          <t>https://artportalen.se/Sighting/136422929</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136422929</v>
+        <v>136422936</v>
       </c>
       <c r="B55" t="n">
         <v>93411</v>
@@ -6461,10 +6454,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687677</v>
+        <v>687703</v>
       </c>
       <c r="R55" t="n">
-        <v>6563484</v>
+        <v>6563526</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6523,13 +6516,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422929</t>
+          <t>https://artportalen.se/Sighting/136422936</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136422936</v>
+        <v>136842796</v>
       </c>
       <c r="B56" t="n">
         <v>93411</v>
@@ -6558,22 +6551,19 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO Norrbytorp, Srm</t>
+          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>687703</v>
+        <v>687649</v>
       </c>
       <c r="R56" t="n">
-        <v>6563526</v>
+        <v>6563389</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6597,12 +6587,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6611,31 +6611,30 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136422936</t>
+          <t>https://artportalen.se/Sighting/136842796</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136842796</v>
+        <v>136842797</v>
       </c>
       <c r="B57" t="n">
         <v>93411</v>
@@ -6670,13 +6669,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>687649</v>
+        <v>687648</v>
       </c>
       <c r="R57" t="n">
-        <v>6563389</v>
+        <v>6563426</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6705,7 +6704,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6715,7 +6714,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6741,16 +6745,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136842796</t>
+          <t>https://artportalen.se/Sighting/136842797</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136842797</v>
+        <v>94982712</v>
       </c>
       <c r="B58" t="n">
-        <v>93411</v>
+        <v>91930</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6758,37 +6762,40 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norrbytorp_inventering_2026-08-30, Srm</t>
+          <t>S Vargklova mosse, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>687648</v>
+        <v>687903</v>
       </c>
       <c r="R58" t="n">
-        <v>6563426</v>
+        <v>6563477</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6812,27 +6819,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:18</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar</t>
+          <t>2021-07-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6841,30 +6833,31 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136842797</t>
+          <t>https://artportalen.se/Sighting/94982712</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>94982712</v>
+        <v>120047138</v>
       </c>
       <c r="B59" t="n">
         <v>91930</v>
@@ -6892,23 +6885,27 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>S Vargklova mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>687903</v>
+        <v>687912</v>
       </c>
       <c r="R59" t="n">
-        <v>6563477</v>
+        <v>6563488</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6932,12 +6929,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6964,13 +6961,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/94982712</t>
+          <t>https://artportalen.se/Sighting/120047138</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120047138</v>
+        <v>129626241</v>
       </c>
       <c r="B60" t="n">
         <v>91930</v>
@@ -7012,10 +7009,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>687912</v>
+        <v>687712</v>
       </c>
       <c r="R60" t="n">
-        <v>6563488</v>
+        <v>6563273</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7042,12 +7039,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I kärrkanten.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7074,16 +7076,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120047138</t>
+          <t>https://artportalen.se/Sighting/129626241</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129626241</v>
+        <v>132642750</v>
       </c>
       <c r="B61" t="n">
-        <v>91930</v>
+        <v>91995</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7108,24 +7110,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>687712</v>
+        <v>687913</v>
       </c>
       <c r="R61" t="n">
-        <v>6563273</v>
+        <v>6563324</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7152,17 +7150,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>I kärrkanten.</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7189,16 +7182,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129626241</t>
+          <t>https://artportalen.se/Sighting/132642750</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132642750</v>
+        <v>136924180</v>
       </c>
       <c r="B62" t="n">
-        <v>91995</v>
+        <v>93437</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7206,21 +7199,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5442</v>
+        <v>5448</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7233,10 +7226,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>687913</v>
+        <v>687734</v>
       </c>
       <c r="R62" t="n">
-        <v>6563324</v>
+        <v>6563371</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7263,12 +7256,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7295,7 +7288,7 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132642750</t>
+          <t>https://artportalen.se/Sighting/136924180</t>
         </is>
       </c>
     </row>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>136801543</v>
       </c>
       <c r="B33" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>136824069</v>
       </c>
       <c r="B34" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>136697189</v>
       </c>
       <c r="B45" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>136422902</v>
       </c>
       <c r="B53" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>136422929</v>
       </c>
       <c r="B54" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136422936</v>
       </c>
       <c r="B55" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>136842796</v>
       </c>
       <c r="B56" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>136842797</v>
       </c>
       <c r="B57" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>136924180</v>
       </c>
       <c r="B62" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>136842798</v>
       </c>
       <c r="B65" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>136823635</v>
       </c>
       <c r="B86" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>136823659</v>
       </c>
       <c r="B87" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>136824686</v>
       </c>
       <c r="B88" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>136843504</v>
       </c>
       <c r="B89" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>136823526</v>
       </c>
       <c r="B92" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>136823927</v>
       </c>
       <c r="B105" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136842963</v>
       </c>
       <c r="B106" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>136941046</v>
       </c>
       <c r="B107" t="n">
-        <v>90859</v>
+        <v>90861</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>136824654</v>
       </c>
       <c r="B108" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>136842826</v>
       </c>
       <c r="B109" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>136842985</v>
       </c>
       <c r="B110" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>136843093</v>
       </c>
       <c r="B111" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>136843333</v>
       </c>
       <c r="B112" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>136823841</v>
       </c>
       <c r="B119" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136823870</v>
       </c>
       <c r="B120" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>136823898</v>
       </c>
       <c r="B121" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>136823966</v>
       </c>
       <c r="B122" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>136823975</v>
       </c>
       <c r="B123" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>136824666</v>
       </c>
       <c r="B124" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>136842642</v>
       </c>
       <c r="B125" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>136842789</v>
       </c>
       <c r="B126" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>136842977</v>
       </c>
       <c r="B127" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>136843078</v>
       </c>
       <c r="B128" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>136843134</v>
       </c>
       <c r="B129" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136842801</v>
       </c>
       <c r="B135" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>136842998</v>
       </c>
       <c r="B138" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>136823791</v>
       </c>
       <c r="B145" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>136823881</v>
       </c>
       <c r="B146" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>136824642</v>
       </c>
       <c r="B147" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136824678</v>
       </c>
       <c r="B148" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>136842702</v>
       </c>
       <c r="B149" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136842790</v>
       </c>
       <c r="B150" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136842972</v>
       </c>
       <c r="B151" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136843073</v>
       </c>
       <c r="B152" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>136843129</v>
       </c>
       <c r="B153" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>136843227</v>
       </c>
       <c r="B154" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>136843356</v>
       </c>
       <c r="B155" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>136843399</v>
       </c>
       <c r="B169" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>136843411</v>
       </c>
       <c r="B183" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>137016225</v>
       </c>
       <c r="B300" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>137016093</v>
       </c>
       <c r="B302" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>137016208</v>
       </c>
       <c r="B303" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>137016378</v>
       </c>
       <c r="B305" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>137016422</v>
       </c>
       <c r="B324" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>137016352</v>
       </c>
       <c r="B403" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>137016265</v>
       </c>
       <c r="B404" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2211,7 +2211,7 @@
         <v>136422957</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>136422980</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>136801543</v>
       </c>
       <c r="B33" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>136824069</v>
       </c>
       <c r="B34" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>136697189</v>
       </c>
       <c r="B45" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>136422902</v>
       </c>
       <c r="B53" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>136422929</v>
       </c>
       <c r="B54" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>136422936</v>
       </c>
       <c r="B55" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>136842796</v>
       </c>
       <c r="B56" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>136842797</v>
       </c>
       <c r="B57" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>136924180</v>
       </c>
       <c r="B62" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>136842798</v>
       </c>
       <c r="B65" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>136823635</v>
       </c>
       <c r="B86" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>136823659</v>
       </c>
       <c r="B87" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>136824686</v>
       </c>
       <c r="B88" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>136843504</v>
       </c>
       <c r="B89" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>136823526</v>
       </c>
       <c r="B92" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>136823927</v>
       </c>
       <c r="B105" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>136842963</v>
       </c>
       <c r="B106" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>136941046</v>
       </c>
       <c r="B107" t="n">
-        <v>90861</v>
+        <v>90863</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>136824654</v>
       </c>
       <c r="B108" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>136842826</v>
       </c>
       <c r="B109" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>136842985</v>
       </c>
       <c r="B110" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>136843093</v>
       </c>
       <c r="B111" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>136843333</v>
       </c>
       <c r="B112" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>136823841</v>
       </c>
       <c r="B119" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>136823870</v>
       </c>
       <c r="B120" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>136823898</v>
       </c>
       <c r="B121" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>136823966</v>
       </c>
       <c r="B122" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>136823975</v>
       </c>
       <c r="B123" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>136824666</v>
       </c>
       <c r="B124" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>136842642</v>
       </c>
       <c r="B125" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>136842789</v>
       </c>
       <c r="B126" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>136842977</v>
       </c>
       <c r="B127" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>136843078</v>
       </c>
       <c r="B128" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>136843134</v>
       </c>
       <c r="B129" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>136842801</v>
       </c>
       <c r="B135" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15430,7 +15430,7 @@
         <v>136842998</v>
       </c>
       <c r="B138" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>136823791</v>
       </c>
       <c r="B145" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>136823881</v>
       </c>
       <c r="B146" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>136824642</v>
       </c>
       <c r="B147" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>136824678</v>
       </c>
       <c r="B148" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>136842702</v>
       </c>
       <c r="B149" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136842790</v>
       </c>
       <c r="B150" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136842972</v>
       </c>
       <c r="B151" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>136843073</v>
       </c>
       <c r="B152" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>136843129</v>
       </c>
       <c r="B153" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>136843227</v>
       </c>
       <c r="B154" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>136843356</v>
       </c>
       <c r="B155" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>136843399</v>
       </c>
       <c r="B169" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>136843411</v>
       </c>
       <c r="B183" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>137016225</v>
       </c>
       <c r="B300" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>137016093</v>
       </c>
       <c r="B302" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>137016208</v>
       </c>
       <c r="B303" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>137016378</v>
       </c>
       <c r="B305" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>137016422</v>
       </c>
       <c r="B324" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>137016352</v>
       </c>
       <c r="B403" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>137016265</v>
       </c>
       <c r="B404" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -11942,7 +11942,7 @@
         <v>137089891</v>
       </c>
       <c r="B106" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136824654</v>
       </c>
       <c r="B131" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136842826</v>
       </c>
       <c r="B132" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136842985</v>
       </c>
       <c r="B133" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>136843093</v>
       </c>
       <c r="B134" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>136843333</v>
       </c>
       <c r="B135" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>137045906</v>
       </c>
       <c r="B193" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>137143034</v>
       </c>
       <c r="B289" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136801543</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136824069</v>
       </c>
       <c r="B37" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         <v>136697189</v>
       </c>
       <c r="B48" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>136842796</v>
       </c>
       <c r="B59" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>136842797</v>
       </c>
       <c r="B60" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>137045903</v>
       </c>
       <c r="B61" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>137045922</v>
       </c>
       <c r="B62" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>137089183</v>
       </c>
       <c r="B63" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         <v>137089291</v>
       </c>
       <c r="B64" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7933,7 +7933,7 @@
         <v>136924180</v>
       </c>
       <c r="B69" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>136842798</v>
       </c>
       <c r="B72" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>137045913</v>
       </c>
       <c r="B73" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>137045925</v>
       </c>
       <c r="B74" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>137045932</v>
       </c>
       <c r="B75" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>137045939</v>
       </c>
       <c r="B76" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>137089303</v>
       </c>
       <c r="B77" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>137089326</v>
       </c>
       <c r="B78" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>137089870</v>
       </c>
       <c r="B79" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>137106221</v>
       </c>
       <c r="B80" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>137106272</v>
       </c>
       <c r="B81" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137144302</v>
       </c>
       <c r="B83" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>137090029</v>
       </c>
       <c r="B101" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>137090074</v>
       </c>
       <c r="B102" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>137144342</v>
       </c>
       <c r="B103" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11942,7 +11942,7 @@
         <v>137089891</v>
       </c>
       <c r="B106" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>136823635</v>
       </c>
       <c r="B109" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         <v>136823659</v>
       </c>
       <c r="B110" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>136824686</v>
       </c>
       <c r="B111" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>136843504</v>
       </c>
       <c r="B112" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>136823526</v>
       </c>
       <c r="B115" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>136823927</v>
       </c>
       <c r="B128" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>136842963</v>
       </c>
       <c r="B129" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>136941046</v>
       </c>
       <c r="B130" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>136824654</v>
       </c>
       <c r="B131" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>136842826</v>
       </c>
       <c r="B132" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>136842985</v>
       </c>
       <c r="B133" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>136843093</v>
       </c>
       <c r="B134" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>136843333</v>
       </c>
       <c r="B135" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>136823841</v>
       </c>
       <c r="B142" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>136823870</v>
       </c>
       <c r="B143" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16058,7 +16058,7 @@
         <v>136823898</v>
       </c>
       <c r="B144" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>136823966</v>
       </c>
       <c r="B145" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>136823975</v>
       </c>
       <c r="B146" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>136824666</v>
       </c>
       <c r="B147" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>136842642</v>
       </c>
       <c r="B148" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>136842789</v>
       </c>
       <c r="B149" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>136842977</v>
       </c>
       <c r="B150" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>136843078</v>
       </c>
       <c r="B151" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>136843134</v>
       </c>
       <c r="B152" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>136842801</v>
       </c>
       <c r="B158" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>136842998</v>
       </c>
       <c r="B161" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>136823791</v>
       </c>
       <c r="B168" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>136823881</v>
       </c>
       <c r="B169" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136824642</v>
       </c>
       <c r="B170" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>136824678</v>
       </c>
       <c r="B171" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>136842702</v>
       </c>
       <c r="B172" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>136842790</v>
       </c>
       <c r="B173" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>136842972</v>
       </c>
       <c r="B174" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>136843073</v>
       </c>
       <c r="B175" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>136843129</v>
       </c>
       <c r="B176" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>136843227</v>
       </c>
       <c r="B177" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>136843356</v>
       </c>
       <c r="B178" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>137107311</v>
       </c>
       <c r="B179" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>137045906</v>
       </c>
       <c r="B193" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>136843399</v>
       </c>
       <c r="B194" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>137106293</v>
       </c>
       <c r="B195" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21682,7 +21682,7 @@
         <v>137106421</v>
       </c>
       <c r="B196" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>137106491</v>
       </c>
       <c r="B197" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>137106521</v>
       </c>
       <c r="B198" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22000,7 +22000,7 @@
         <v>137106571</v>
       </c>
       <c r="B199" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>137106348</v>
       </c>
       <c r="B210" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>137106366</v>
       </c>
       <c r="B211" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>137106378</v>
       </c>
       <c r="B212" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>137106442</v>
       </c>
       <c r="B213" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>137106474</v>
       </c>
       <c r="B214" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>137106502</v>
       </c>
       <c r="B215" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>137144390</v>
       </c>
       <c r="B216" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23921,7 +23921,7 @@
         <v>137144403</v>
       </c>
       <c r="B217" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>137144419</v>
       </c>
       <c r="B218" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>137144429</v>
       </c>
       <c r="B219" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>136843411</v>
       </c>
       <c r="B223" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>137144374</v>
       </c>
       <c r="B236" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27961,7 +27961,7 @@
         <v>137143190</v>
       </c>
       <c r="B254" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>137143205</v>
       </c>
       <c r="B255" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>137143230</v>
       </c>
       <c r="B256" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>137144549</v>
       </c>
       <c r="B257" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>137143034</v>
       </c>
       <c r="B289" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32600,7 +32600,7 @@
         <v>137124255</v>
       </c>
       <c r="B297" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32706,7 +32706,7 @@
         <v>137142668</v>
       </c>
       <c r="B298" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32812,7 +32812,7 @@
         <v>137142944</v>
       </c>
       <c r="B299" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>137143162</v>
       </c>
       <c r="B300" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>137143048</v>
       </c>
       <c r="B304" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>137142760</v>
       </c>
       <c r="B307" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>137142797</v>
       </c>
       <c r="B308" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>137107280</v>
       </c>
       <c r="B316" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34740,7 +34740,7 @@
         <v>137124150</v>
       </c>
       <c r="B317" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>137124193</v>
       </c>
       <c r="B318" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>137142713</v>
       </c>
       <c r="B319" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>137142721</v>
       </c>
       <c r="B320" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35164,7 +35164,7 @@
         <v>137142731</v>
       </c>
       <c r="B321" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35270,7 +35270,7 @@
         <v>137142818</v>
       </c>
       <c r="B322" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35376,7 +35376,7 @@
         <v>137142840</v>
       </c>
       <c r="B323" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>137143060</v>
       </c>
       <c r="B324" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>137143076</v>
       </c>
       <c r="B325" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>137143137</v>
       </c>
       <c r="B326" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35800,7 +35800,7 @@
         <v>137143177</v>
       </c>
       <c r="B327" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>137107090</v>
       </c>
       <c r="B348" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -38509,7 +38509,7 @@
         <v>137106534</v>
       </c>
       <c r="B352" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>137106671</v>
       </c>
       <c r="B353" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>137107185</v>
       </c>
       <c r="B354" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>137106597</v>
       </c>
       <c r="B355" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>137106552</v>
       </c>
       <c r="B361" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>137106662</v>
       </c>
       <c r="B362" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>137107145</v>
       </c>
       <c r="B363" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>137107170</v>
       </c>
       <c r="B364" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39901,7 +39901,7 @@
         <v>137107199</v>
       </c>
       <c r="B365" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>137107238</v>
       </c>
       <c r="B366" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>137107267</v>
       </c>
       <c r="B367" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>137107297</v>
       </c>
       <c r="B368" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>137142621</v>
       </c>
       <c r="B369" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41642,7 +41642,7 @@
         <v>137016225</v>
       </c>
       <c r="B381" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -41859,7 +41859,7 @@
         <v>137016093</v>
       </c>
       <c r="B383" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -41965,7 +41965,7 @@
         <v>137016208</v>
       </c>
       <c r="B384" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -42177,7 +42177,7 @@
         <v>137016378</v>
       </c>
       <c r="B386" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44300,7 +44300,7 @@
         <v>137016422</v>
       </c>
       <c r="B405" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>137123693</v>
       </c>
       <c r="B413" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>137143246</v>
       </c>
       <c r="B414" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -45367,7 +45367,7 @@
         <v>137144503</v>
       </c>
       <c r="B415" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>137144527</v>
       </c>
       <c r="B416" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -46546,7 +46546,7 @@
         <v>137124073</v>
       </c>
       <c r="B426" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -46864,7 +46864,7 @@
         <v>137123623</v>
       </c>
       <c r="B429" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -46970,7 +46970,7 @@
         <v>137123636</v>
       </c>
       <c r="B430" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>137123709</v>
       </c>
       <c r="B431" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>137123822</v>
       </c>
       <c r="B432" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>137123842</v>
       </c>
       <c r="B433" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>137123906</v>
       </c>
       <c r="B434" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>137124052</v>
       </c>
       <c r="B435" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>137144483</v>
       </c>
       <c r="B457" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>137144492</v>
       </c>
       <c r="B458" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>137016352</v>
       </c>
       <c r="B500" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>137016265</v>
       </c>
       <c r="B501" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136801543</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136824069</v>
       </c>
       <c r="B37" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>136842796</v>
       </c>
       <c r="B59" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>136842797</v>
       </c>
       <c r="B60" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>137045903</v>
       </c>
       <c r="B61" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045922</v>
       </c>
       <c r="B62" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137089183</v>
       </c>
       <c r="B63" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089291</v>
       </c>
       <c r="B64" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>136924180</v>
       </c>
       <c r="B69" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>136842798</v>
       </c>
       <c r="B72" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>137045913</v>
       </c>
       <c r="B73" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045925</v>
       </c>
       <c r="B74" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045932</v>
       </c>
       <c r="B75" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045939</v>
       </c>
       <c r="B76" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137089303</v>
       </c>
       <c r="B77" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089326</v>
       </c>
       <c r="B78" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089870</v>
       </c>
       <c r="B79" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137106221</v>
       </c>
       <c r="B80" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106272</v>
       </c>
       <c r="B81" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144302</v>
       </c>
       <c r="B83" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>137045899</v>
       </c>
       <c r="B90" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>137090029</v>
       </c>
       <c r="B101" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090074</v>
       </c>
       <c r="B102" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137144342</v>
       </c>
       <c r="B103" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>137089891</v>
       </c>
       <c r="B106" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>136823635</v>
       </c>
       <c r="B109" t="n">
-        <v>90894</v>
+        <v>90904</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136823659</v>
       </c>
       <c r="B110" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>136824686</v>
       </c>
       <c r="B111" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136843504</v>
       </c>
       <c r="B112" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>136823526</v>
       </c>
       <c r="B115" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>136842628</v>
       </c>
       <c r="B117" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>136823927</v>
       </c>
       <c r="B128" t="n">
-        <v>90894</v>
+        <v>90904</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>136842963</v>
       </c>
       <c r="B129" t="n">
-        <v>90894</v>
+        <v>90904</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136941046</v>
       </c>
       <c r="B130" t="n">
-        <v>90894</v>
+        <v>90904</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>136824654</v>
       </c>
       <c r="B131" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>136842826</v>
       </c>
       <c r="B132" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>136842985</v>
       </c>
       <c r="B133" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>136843093</v>
       </c>
       <c r="B134" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>136843333</v>
       </c>
       <c r="B135" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>136823841</v>
       </c>
       <c r="B142" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>136823870</v>
       </c>
       <c r="B143" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>136823898</v>
       </c>
       <c r="B144" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>136823966</v>
       </c>
       <c r="B145" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>136823975</v>
       </c>
       <c r="B146" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>136824666</v>
       </c>
       <c r="B147" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136842642</v>
       </c>
       <c r="B148" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>136842789</v>
       </c>
       <c r="B149" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>136842977</v>
       </c>
       <c r="B150" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>136843078</v>
       </c>
       <c r="B151" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>136843134</v>
       </c>
       <c r="B152" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>136842801</v>
       </c>
       <c r="B158" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>136842998</v>
       </c>
       <c r="B161" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>136823791</v>
       </c>
       <c r="B168" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>136823881</v>
       </c>
       <c r="B169" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>136824642</v>
       </c>
       <c r="B170" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>136824678</v>
       </c>
       <c r="B171" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>136842702</v>
       </c>
       <c r="B172" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136842790</v>
       </c>
       <c r="B173" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136842972</v>
       </c>
       <c r="B174" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>136843073</v>
       </c>
       <c r="B175" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>136843129</v>
       </c>
       <c r="B176" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>136843227</v>
       </c>
       <c r="B177" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136843356</v>
       </c>
       <c r="B178" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>137107311</v>
       </c>
       <c r="B179" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>136823813</v>
       </c>
       <c r="B184" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137045906</v>
       </c>
       <c r="B193" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>136843399</v>
       </c>
       <c r="B194" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>137106293</v>
       </c>
       <c r="B195" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106421</v>
       </c>
       <c r="B196" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106491</v>
       </c>
       <c r="B197" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106521</v>
       </c>
       <c r="B198" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106571</v>
       </c>
       <c r="B199" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>137106348</v>
       </c>
       <c r="B210" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106366</v>
       </c>
       <c r="B211" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106378</v>
       </c>
       <c r="B212" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106442</v>
       </c>
       <c r="B213" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106474</v>
       </c>
       <c r="B214" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106502</v>
       </c>
       <c r="B215" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137144390</v>
       </c>
       <c r="B216" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144403</v>
       </c>
       <c r="B217" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144419</v>
       </c>
       <c r="B218" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144429</v>
       </c>
       <c r="B219" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>136843411</v>
       </c>
       <c r="B223" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>137144356</v>
       </c>
       <c r="B229" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>137106314</v>
       </c>
       <c r="B231" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>137144374</v>
       </c>
       <c r="B236" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>137143190</v>
       </c>
       <c r="B254" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>137143205</v>
       </c>
       <c r="B255" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143230</v>
       </c>
       <c r="B256" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137144549</v>
       </c>
       <c r="B257" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>137143034</v>
       </c>
       <c r="B289" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>137124255</v>
       </c>
       <c r="B297" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>137142668</v>
       </c>
       <c r="B298" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137142944</v>
       </c>
       <c r="B299" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137143162</v>
       </c>
       <c r="B300" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>137143048</v>
       </c>
       <c r="B304" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>137142760</v>
       </c>
       <c r="B307" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>137142797</v>
       </c>
       <c r="B308" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>137107280</v>
       </c>
       <c r="B316" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>137124150</v>
       </c>
       <c r="B317" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137124193</v>
       </c>
       <c r="B318" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137142713</v>
       </c>
       <c r="B319" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137142721</v>
       </c>
       <c r="B320" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142731</v>
       </c>
       <c r="B321" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142818</v>
       </c>
       <c r="B322" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142840</v>
       </c>
       <c r="B323" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137143060</v>
       </c>
       <c r="B324" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137143076</v>
       </c>
       <c r="B325" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143137</v>
       </c>
       <c r="B326" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143177</v>
       </c>
       <c r="B327" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>137107090</v>
       </c>
       <c r="B348" t="n">
-        <v>90894</v>
+        <v>90904</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>137106534</v>
       </c>
       <c r="B352" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>137106671</v>
       </c>
       <c r="B353" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137107185</v>
       </c>
       <c r="B354" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106597</v>
       </c>
       <c r="B355" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>137106552</v>
       </c>
       <c r="B361" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>137106662</v>
       </c>
       <c r="B362" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137107145</v>
       </c>
       <c r="B363" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137107170</v>
       </c>
       <c r="B364" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107199</v>
       </c>
       <c r="B365" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107238</v>
       </c>
       <c r="B366" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107267</v>
       </c>
       <c r="B367" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107297</v>
       </c>
       <c r="B368" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137142621</v>
       </c>
       <c r="B369" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>137016225</v>
       </c>
       <c r="B381" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>137016093</v>
       </c>
       <c r="B383" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>137016208</v>
       </c>
       <c r="B384" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016378</v>
       </c>
       <c r="B386" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>137016422</v>
       </c>
       <c r="B405" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>137123693</v>
       </c>
       <c r="B413" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>137143246</v>
       </c>
       <c r="B414" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>137144503</v>
       </c>
       <c r="B415" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137144527</v>
       </c>
       <c r="B416" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>137124073</v>
       </c>
       <c r="B426" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137123623</v>
       </c>
       <c r="B429" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>137123636</v>
       </c>
       <c r="B430" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>137123709</v>
       </c>
       <c r="B431" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123822</v>
       </c>
       <c r="B432" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123842</v>
       </c>
       <c r="B433" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123906</v>
       </c>
       <c r="B434" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137124052</v>
       </c>
       <c r="B435" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137290863</v>
       </c>
       <c r="B436" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137291623</v>
       </c>
       <c r="B437" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>137123759</v>
       </c>
       <c r="B444" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>137124010</v>
       </c>
       <c r="B445" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>137291594</v>
       </c>
       <c r="B459" t="n">
-        <v>93441</v>
+        <v>93451</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>137144483</v>
       </c>
       <c r="B460" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>137144492</v>
       </c>
       <c r="B461" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>137016352</v>
       </c>
       <c r="B503" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>137016265</v>
       </c>
       <c r="B504" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>137290686</v>
       </c>
       <c r="B542" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         <v>137291317</v>
       </c>
       <c r="B548" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>137291210</v>
       </c>
       <c r="B552" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>137290838</v>
       </c>
       <c r="B556" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -60970,7 +60970,7 @@
         <v>137290848</v>
       </c>
       <c r="B557" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>137290857</v>
       </c>
       <c r="B558" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>137291218</v>
       </c>
       <c r="B559" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -61288,7 +61288,7 @@
         <v>137291263</v>
       </c>
       <c r="B560" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>137238726</v>
       </c>
       <c r="B591" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65142,7 +65142,7 @@
         <v>137240254</v>
       </c>
       <c r="B595" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -65937,7 +65937,7 @@
         <v>137290579</v>
       </c>
       <c r="B602" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>137290591</v>
       </c>
       <c r="B608" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
         <v>137290729</v>
       </c>
       <c r="B612" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -67163,7 +67163,7 @@
         <v>137290756</v>
       </c>
       <c r="B613" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -67269,7 +67269,7 @@
         <v>137290815</v>
       </c>
       <c r="B614" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -69796,7 +69796,7 @@
         <v>137240024</v>
       </c>
       <c r="B637" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -69902,7 +69902,7 @@
         <v>137240039</v>
       </c>
       <c r="B638" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>137238841</v>
       </c>
       <c r="B646" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -70885,7 +70885,7 @@
         <v>137238858</v>
       </c>
       <c r="B647" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>137240141</v>
       </c>
       <c r="B648" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -71448,7 +71448,7 @@
         <v>137240203</v>
       </c>
       <c r="B652" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -71670,7 +71670,7 @@
         <v>137238811</v>
       </c>
       <c r="B654" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -73848,7 +73848,7 @@
         <v>137239472</v>
       </c>
       <c r="B674" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -73954,7 +73954,7 @@
         <v>137239964</v>
       </c>
       <c r="B675" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -74060,7 +74060,7 @@
         <v>137240074</v>
       </c>
       <c r="B676" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -75046,7 +75046,7 @@
         <v>137239535</v>
       </c>
       <c r="B685" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -75152,7 +75152,7 @@
         <v>137239564</v>
       </c>
       <c r="B686" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -75258,7 +75258,7 @@
         <v>137239989</v>
       </c>
       <c r="B687" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -76140,7 +76140,7 @@
         <v>137239483</v>
       </c>
       <c r="B695" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -76246,7 +76246,7 @@
         <v>137239495</v>
       </c>
       <c r="B696" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -76895,7 +76895,7 @@
         <v>137240122</v>
       </c>
       <c r="B702" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -77213,7 +77213,7 @@
         <v>137238959</v>
       </c>
       <c r="B705" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -77319,7 +77319,7 @@
         <v>137238973</v>
       </c>
       <c r="B706" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -77425,7 +77425,7 @@
         <v>137238992</v>
       </c>
       <c r="B707" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -77531,7 +77531,7 @@
         <v>137239263</v>
       </c>
       <c r="B708" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -77637,7 +77637,7 @@
         <v>137239323</v>
       </c>
       <c r="B709" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -77743,7 +77743,7 @@
         <v>137240084</v>
       </c>
       <c r="B710" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -78644,7 +78644,7 @@
         <v>137239011</v>
       </c>
       <c r="B718" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -78750,7 +78750,7 @@
         <v>137239194</v>
       </c>
       <c r="B719" t="n">
-        <v>98259</v>
+        <v>98269</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136801543</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136824069</v>
       </c>
       <c r="B37" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>136842796</v>
       </c>
       <c r="B59" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>136842797</v>
       </c>
       <c r="B60" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>137045903</v>
       </c>
       <c r="B61" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045922</v>
       </c>
       <c r="B62" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137089183</v>
       </c>
       <c r="B63" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089291</v>
       </c>
       <c r="B64" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>136924180</v>
       </c>
       <c r="B69" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>136842798</v>
       </c>
       <c r="B72" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>137045913</v>
       </c>
       <c r="B73" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045925</v>
       </c>
       <c r="B74" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045932</v>
       </c>
       <c r="B75" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045939</v>
       </c>
       <c r="B76" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137089303</v>
       </c>
       <c r="B77" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089326</v>
       </c>
       <c r="B78" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089870</v>
       </c>
       <c r="B79" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137106221</v>
       </c>
       <c r="B80" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106272</v>
       </c>
       <c r="B81" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144302</v>
       </c>
       <c r="B83" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>137090029</v>
       </c>
       <c r="B101" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090074</v>
       </c>
       <c r="B102" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137144342</v>
       </c>
       <c r="B103" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>137089891</v>
       </c>
       <c r="B106" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>136823635</v>
       </c>
       <c r="B109" t="n">
-        <v>90904</v>
+        <v>90905</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136823659</v>
       </c>
       <c r="B110" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>136824686</v>
       </c>
       <c r="B111" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136843504</v>
       </c>
       <c r="B112" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>136823526</v>
       </c>
       <c r="B115" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>136823927</v>
       </c>
       <c r="B128" t="n">
-        <v>90904</v>
+        <v>90905</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>136842963</v>
       </c>
       <c r="B129" t="n">
-        <v>90904</v>
+        <v>90905</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136941046</v>
       </c>
       <c r="B130" t="n">
-        <v>90904</v>
+        <v>90905</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>136824654</v>
       </c>
       <c r="B131" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>136842826</v>
       </c>
       <c r="B132" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>136842985</v>
       </c>
       <c r="B133" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>136843093</v>
       </c>
       <c r="B134" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>136843333</v>
       </c>
       <c r="B135" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>136823841</v>
       </c>
       <c r="B142" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>136823870</v>
       </c>
       <c r="B143" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>136823898</v>
       </c>
       <c r="B144" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>136823966</v>
       </c>
       <c r="B145" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>136823975</v>
       </c>
       <c r="B146" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>136824666</v>
       </c>
       <c r="B147" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136842642</v>
       </c>
       <c r="B148" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>136842789</v>
       </c>
       <c r="B149" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>136842977</v>
       </c>
       <c r="B150" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>136843078</v>
       </c>
       <c r="B151" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>136843134</v>
       </c>
       <c r="B152" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>136842801</v>
       </c>
       <c r="B158" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>136842998</v>
       </c>
       <c r="B161" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>136823791</v>
       </c>
       <c r="B168" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>136823881</v>
       </c>
       <c r="B169" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>136824642</v>
       </c>
       <c r="B170" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>136824678</v>
       </c>
       <c r="B171" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>136842702</v>
       </c>
       <c r="B172" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136842790</v>
       </c>
       <c r="B173" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136842972</v>
       </c>
       <c r="B174" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>136843073</v>
       </c>
       <c r="B175" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>136843129</v>
       </c>
       <c r="B176" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>136843227</v>
       </c>
       <c r="B177" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136843356</v>
       </c>
       <c r="B178" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>137107311</v>
       </c>
       <c r="B179" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137045906</v>
       </c>
       <c r="B193" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>136843399</v>
       </c>
       <c r="B194" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>137106293</v>
       </c>
       <c r="B195" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106421</v>
       </c>
       <c r="B196" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106491</v>
       </c>
       <c r="B197" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106521</v>
       </c>
       <c r="B198" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106571</v>
       </c>
       <c r="B199" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>137106348</v>
       </c>
       <c r="B210" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106366</v>
       </c>
       <c r="B211" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106378</v>
       </c>
       <c r="B212" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106442</v>
       </c>
       <c r="B213" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106474</v>
       </c>
       <c r="B214" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106502</v>
       </c>
       <c r="B215" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137144390</v>
       </c>
       <c r="B216" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144403</v>
       </c>
       <c r="B217" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144419</v>
       </c>
       <c r="B218" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144429</v>
       </c>
       <c r="B219" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>136843411</v>
       </c>
       <c r="B223" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>137144374</v>
       </c>
       <c r="B236" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>137143190</v>
       </c>
       <c r="B254" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>137143205</v>
       </c>
       <c r="B255" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143230</v>
       </c>
       <c r="B256" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137144549</v>
       </c>
       <c r="B257" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>137143034</v>
       </c>
       <c r="B289" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>137124255</v>
       </c>
       <c r="B297" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>137142668</v>
       </c>
       <c r="B298" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137142944</v>
       </c>
       <c r="B299" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137143162</v>
       </c>
       <c r="B300" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>137143048</v>
       </c>
       <c r="B304" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>137142760</v>
       </c>
       <c r="B307" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>137142797</v>
       </c>
       <c r="B308" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>137107280</v>
       </c>
       <c r="B316" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>137124150</v>
       </c>
       <c r="B317" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137124193</v>
       </c>
       <c r="B318" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137142713</v>
       </c>
       <c r="B319" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137142721</v>
       </c>
       <c r="B320" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142731</v>
       </c>
       <c r="B321" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142818</v>
       </c>
       <c r="B322" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142840</v>
       </c>
       <c r="B323" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137143060</v>
       </c>
       <c r="B324" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137143076</v>
       </c>
       <c r="B325" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143137</v>
       </c>
       <c r="B326" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143177</v>
       </c>
       <c r="B327" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>137107090</v>
       </c>
       <c r="B348" t="n">
-        <v>90904</v>
+        <v>90905</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>137106534</v>
       </c>
       <c r="B352" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>137106671</v>
       </c>
       <c r="B353" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137107185</v>
       </c>
       <c r="B354" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106597</v>
       </c>
       <c r="B355" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>137106552</v>
       </c>
       <c r="B361" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>137106662</v>
       </c>
       <c r="B362" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137107145</v>
       </c>
       <c r="B363" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137107170</v>
       </c>
       <c r="B364" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107199</v>
       </c>
       <c r="B365" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107238</v>
       </c>
       <c r="B366" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107267</v>
       </c>
       <c r="B367" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107297</v>
       </c>
       <c r="B368" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137142621</v>
       </c>
       <c r="B369" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>137016225</v>
       </c>
       <c r="B381" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>137016093</v>
       </c>
       <c r="B383" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>137016208</v>
       </c>
       <c r="B384" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016378</v>
       </c>
       <c r="B386" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>137016422</v>
       </c>
       <c r="B405" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>137123693</v>
       </c>
       <c r="B413" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>137143246</v>
       </c>
       <c r="B414" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>137144503</v>
       </c>
       <c r="B415" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137144527</v>
       </c>
       <c r="B416" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>137124073</v>
       </c>
       <c r="B426" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137123623</v>
       </c>
       <c r="B429" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>137123636</v>
       </c>
       <c r="B430" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>137123709</v>
       </c>
       <c r="B431" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123822</v>
       </c>
       <c r="B432" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123842</v>
       </c>
       <c r="B433" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123906</v>
       </c>
       <c r="B434" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137124052</v>
       </c>
       <c r="B435" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137290863</v>
       </c>
       <c r="B436" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137291623</v>
       </c>
       <c r="B437" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>137291594</v>
       </c>
       <c r="B459" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>137144483</v>
       </c>
       <c r="B460" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>137144492</v>
       </c>
       <c r="B461" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -55005,7 +55005,7 @@
         <v>137016352</v>
       </c>
       <c r="B503" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -55111,7 +55111,7 @@
         <v>137016265</v>
       </c>
       <c r="B504" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>137290686</v>
       </c>
       <c r="B542" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         <v>137291317</v>
       </c>
       <c r="B548" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -60436,7 +60436,7 @@
         <v>137291210</v>
       </c>
       <c r="B552" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -60864,7 +60864,7 @@
         <v>137290838</v>
       </c>
       <c r="B556" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -60970,7 +60970,7 @@
         <v>137290848</v>
       </c>
       <c r="B557" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>137290857</v>
       </c>
       <c r="B558" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>137291218</v>
       </c>
       <c r="B559" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -61288,7 +61288,7 @@
         <v>137291263</v>
       </c>
       <c r="B560" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>137238726</v>
       </c>
       <c r="B591" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65937,7 +65937,7 @@
         <v>137290579</v>
       </c>
       <c r="B602" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -66633,7 +66633,7 @@
         <v>137290591</v>
       </c>
       <c r="B608" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -67057,7 +67057,7 @@
         <v>137290729</v>
       </c>
       <c r="B612" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -67163,7 +67163,7 @@
         <v>137290756</v>
       </c>
       <c r="B613" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -69796,7 +69796,7 @@
         <v>137240024</v>
       </c>
       <c r="B637" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -69902,7 +69902,7 @@
         <v>137240039</v>
       </c>
       <c r="B638" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -70779,7 +70779,7 @@
         <v>137238841</v>
       </c>
       <c r="B646" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -70885,7 +70885,7 @@
         <v>137238858</v>
       </c>
       <c r="B647" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -70991,7 +70991,7 @@
         <v>137240141</v>
       </c>
       <c r="B648" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -71448,7 +71448,7 @@
         <v>137240203</v>
       </c>
       <c r="B652" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -71670,7 +71670,7 @@
         <v>137238811</v>
       </c>
       <c r="B654" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -73848,7 +73848,7 @@
         <v>137239472</v>
       </c>
       <c r="B674" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -73954,7 +73954,7 @@
         <v>137239964</v>
       </c>
       <c r="B675" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -74060,7 +74060,7 @@
         <v>137240074</v>
       </c>
       <c r="B676" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -75046,7 +75046,7 @@
         <v>137239535</v>
       </c>
       <c r="B685" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -75152,7 +75152,7 @@
         <v>137239564</v>
       </c>
       <c r="B686" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -75258,7 +75258,7 @@
         <v>137239989</v>
       </c>
       <c r="B687" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -76895,7 +76895,7 @@
         <v>137240122</v>
       </c>
       <c r="B702" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -77213,7 +77213,7 @@
         <v>137238959</v>
       </c>
       <c r="B705" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -77319,7 +77319,7 @@
         <v>137238973</v>
       </c>
       <c r="B706" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -77425,7 +77425,7 @@
         <v>137238992</v>
       </c>
       <c r="B707" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -77531,7 +77531,7 @@
         <v>137239263</v>
       </c>
       <c r="B708" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -77637,7 +77637,7 @@
         <v>137239323</v>
       </c>
       <c r="B709" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -77743,7 +77743,7 @@
         <v>137240084</v>
       </c>
       <c r="B710" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -78750,7 +78750,7 @@
         <v>137239194</v>
       </c>
       <c r="B719" t="n">
-        <v>98269</v>
+        <v>98270</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136801543</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136824069</v>
       </c>
       <c r="B37" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>136842796</v>
       </c>
       <c r="B59" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>136842797</v>
       </c>
       <c r="B60" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>137045903</v>
       </c>
       <c r="B61" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045922</v>
       </c>
       <c r="B62" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137089183</v>
       </c>
       <c r="B63" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089291</v>
       </c>
       <c r="B64" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>136924180</v>
       </c>
       <c r="B69" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>136842798</v>
       </c>
       <c r="B72" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>137045913</v>
       </c>
       <c r="B73" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045925</v>
       </c>
       <c r="B74" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045932</v>
       </c>
       <c r="B75" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045939</v>
       </c>
       <c r="B76" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137089303</v>
       </c>
       <c r="B77" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089326</v>
       </c>
       <c r="B78" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089870</v>
       </c>
       <c r="B79" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137106221</v>
       </c>
       <c r="B80" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106272</v>
       </c>
       <c r="B81" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144302</v>
       </c>
       <c r="B83" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>137090029</v>
       </c>
       <c r="B101" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090074</v>
       </c>
       <c r="B102" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137144342</v>
       </c>
       <c r="B103" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>137089891</v>
       </c>
       <c r="B106" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136823659</v>
       </c>
       <c r="B110" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>136824686</v>
       </c>
       <c r="B111" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136843504</v>
       </c>
       <c r="B112" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>136823526</v>
       </c>
       <c r="B115" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>136824654</v>
       </c>
       <c r="B131" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>136842826</v>
       </c>
       <c r="B132" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>136842985</v>
       </c>
       <c r="B133" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>136843093</v>
       </c>
       <c r="B134" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>136843333</v>
       </c>
       <c r="B135" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>136823841</v>
       </c>
       <c r="B142" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>136823870</v>
       </c>
       <c r="B143" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>136823898</v>
       </c>
       <c r="B144" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>136823966</v>
       </c>
       <c r="B145" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>136823975</v>
       </c>
       <c r="B146" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>136824666</v>
       </c>
       <c r="B147" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136842642</v>
       </c>
       <c r="B148" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>136842789</v>
       </c>
       <c r="B149" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>136842977</v>
       </c>
       <c r="B150" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>136843078</v>
       </c>
       <c r="B151" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>136843134</v>
       </c>
       <c r="B152" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>136842801</v>
       </c>
       <c r="B158" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>136842998</v>
       </c>
       <c r="B161" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>136823791</v>
       </c>
       <c r="B168" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>136823881</v>
       </c>
       <c r="B169" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>136824642</v>
       </c>
       <c r="B170" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>136824678</v>
       </c>
       <c r="B171" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>136842702</v>
       </c>
       <c r="B172" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136842790</v>
       </c>
       <c r="B173" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136842972</v>
       </c>
       <c r="B174" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>136843073</v>
       </c>
       <c r="B175" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>136843129</v>
       </c>
       <c r="B176" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>136843227</v>
       </c>
       <c r="B177" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136843356</v>
       </c>
       <c r="B178" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>137107311</v>
       </c>
       <c r="B179" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137045906</v>
       </c>
       <c r="B193" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>136843399</v>
       </c>
       <c r="B194" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>137106293</v>
       </c>
       <c r="B195" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106421</v>
       </c>
       <c r="B196" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106491</v>
       </c>
       <c r="B197" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106521</v>
       </c>
       <c r="B198" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106571</v>
       </c>
       <c r="B199" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>137106348</v>
       </c>
       <c r="B210" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106366</v>
       </c>
       <c r="B211" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106378</v>
       </c>
       <c r="B212" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106442</v>
       </c>
       <c r="B213" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106474</v>
       </c>
       <c r="B214" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106502</v>
       </c>
       <c r="B215" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137144390</v>
       </c>
       <c r="B216" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144403</v>
       </c>
       <c r="B217" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144419</v>
       </c>
       <c r="B218" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144429</v>
       </c>
       <c r="B219" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>136843411</v>
       </c>
       <c r="B223" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>137144374</v>
       </c>
       <c r="B236" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>137143190</v>
       </c>
       <c r="B254" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>137143205</v>
       </c>
       <c r="B255" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143230</v>
       </c>
       <c r="B256" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137144549</v>
       </c>
       <c r="B257" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>137143034</v>
       </c>
       <c r="B289" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>137124255</v>
       </c>
       <c r="B297" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>137142668</v>
       </c>
       <c r="B298" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137142944</v>
       </c>
       <c r="B299" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137143162</v>
       </c>
       <c r="B300" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>137143048</v>
       </c>
       <c r="B304" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>137142760</v>
       </c>
       <c r="B307" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>137142797</v>
       </c>
       <c r="B308" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>137107280</v>
       </c>
       <c r="B316" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>137124150</v>
       </c>
       <c r="B317" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137124193</v>
       </c>
       <c r="B318" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137142713</v>
       </c>
       <c r="B319" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137142721</v>
       </c>
       <c r="B320" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142731</v>
       </c>
       <c r="B321" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142818</v>
       </c>
       <c r="B322" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142840</v>
       </c>
       <c r="B323" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137143060</v>
       </c>
       <c r="B324" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137143076</v>
       </c>
       <c r="B325" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143137</v>
       </c>
       <c r="B326" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143177</v>
       </c>
       <c r="B327" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>137106534</v>
       </c>
       <c r="B352" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>137106671</v>
       </c>
       <c r="B353" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137107185</v>
       </c>
       <c r="B354" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106597</v>
       </c>
       <c r="B355" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>137106552</v>
       </c>
       <c r="B361" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>137106662</v>
       </c>
       <c r="B362" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137107145</v>
       </c>
       <c r="B363" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137107170</v>
       </c>
       <c r="B364" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107199</v>
       </c>
       <c r="B365" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107238</v>
       </c>
       <c r="B366" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107267</v>
       </c>
       <c r="B367" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107297</v>
       </c>
       <c r="B368" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137142621</v>
       </c>
       <c r="B369" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>137016225</v>
       </c>
       <c r="B381" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>137016093</v>
       </c>
       <c r="B383" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>137016208</v>
       </c>
       <c r="B384" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016378</v>
       </c>
       <c r="B386" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>137016422</v>
       </c>
       <c r="B405" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>137123693</v>
       </c>
       <c r="B413" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>137143246</v>
       </c>
       <c r="B414" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>137144503</v>
       </c>
       <c r="B415" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137144527</v>
       </c>
       <c r="B416" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>137124073</v>
       </c>
       <c r="B426" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137123623</v>
       </c>
       <c r="B429" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>137123636</v>
       </c>
       <c r="B430" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>137123709</v>
       </c>
       <c r="B431" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123822</v>
       </c>
       <c r="B432" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123842</v>
       </c>
       <c r="B433" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123906</v>
       </c>
       <c r="B434" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137124052</v>
       </c>
       <c r="B435" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137290863</v>
       </c>
       <c r="B436" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137291615</v>
       </c>
       <c r="B437" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>137291623</v>
       </c>
       <c r="B438" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>137291594</v>
       </c>
       <c r="B460" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>137144483</v>
       </c>
       <c r="B461" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>137144492</v>
       </c>
       <c r="B462" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>137291563</v>
       </c>
       <c r="B463" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>137291571</v>
       </c>
       <c r="B464" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>137016352</v>
       </c>
       <c r="B506" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -55429,7 +55429,7 @@
         <v>137016265</v>
       </c>
       <c r="B507" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>137290686</v>
       </c>
       <c r="B545" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -60316,7 +60316,7 @@
         <v>137291317</v>
       </c>
       <c r="B551" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -60754,7 +60754,7 @@
         <v>137291210</v>
       </c>
       <c r="B555" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>137290838</v>
       </c>
       <c r="B559" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -61288,7 +61288,7 @@
         <v>137290848</v>
       </c>
       <c r="B560" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>137290857</v>
       </c>
       <c r="B561" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>137291070</v>
       </c>
       <c r="B562" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>137291162</v>
       </c>
       <c r="B563" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>137291186</v>
       </c>
       <c r="B564" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>137291193</v>
       </c>
       <c r="B565" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>137291218</v>
       </c>
       <c r="B566" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>137291263</v>
       </c>
       <c r="B567" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -62141,7 +62141,7 @@
         <v>137291298</v>
       </c>
       <c r="B568" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>137291402</v>
       </c>
       <c r="B569" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>137291412</v>
       </c>
       <c r="B570" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>137291421</v>
       </c>
       <c r="B571" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>137291426</v>
       </c>
       <c r="B589" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>137291430</v>
       </c>
       <c r="B590" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -64667,7 +64667,7 @@
         <v>137291534</v>
       </c>
       <c r="B591" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>137291554</v>
       </c>
       <c r="B592" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>137238726</v>
       </c>
       <c r="B606" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -67527,7 +67527,7 @@
         <v>137290579</v>
       </c>
       <c r="B617" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -68223,7 +68223,7 @@
         <v>137290591</v>
       </c>
       <c r="B623" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>137290729</v>
       </c>
       <c r="B627" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -68753,7 +68753,7 @@
         <v>137290756</v>
       </c>
       <c r="B628" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>137240024</v>
       </c>
       <c r="B652" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -71492,7 +71492,7 @@
         <v>137240039</v>
       </c>
       <c r="B653" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -72369,7 +72369,7 @@
         <v>137238841</v>
       </c>
       <c r="B661" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -72475,7 +72475,7 @@
         <v>137238858</v>
       </c>
       <c r="B662" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -72581,7 +72581,7 @@
         <v>137240141</v>
       </c>
       <c r="B663" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>137240203</v>
       </c>
       <c r="B667" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -73260,7 +73260,7 @@
         <v>137238811</v>
       </c>
       <c r="B669" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -75438,7 +75438,7 @@
         <v>137239472</v>
       </c>
       <c r="B689" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -75544,7 +75544,7 @@
         <v>137239964</v>
       </c>
       <c r="B690" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -75650,7 +75650,7 @@
         <v>137240074</v>
       </c>
       <c r="B691" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>137239535</v>
       </c>
       <c r="B700" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -76742,7 +76742,7 @@
         <v>137239564</v>
       </c>
       <c r="B701" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -76848,7 +76848,7 @@
         <v>137239989</v>
       </c>
       <c r="B702" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -78485,7 +78485,7 @@
         <v>137240122</v>
       </c>
       <c r="B717" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -78803,7 +78803,7 @@
         <v>137238959</v>
       </c>
       <c r="B720" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -78909,7 +78909,7 @@
         <v>137238973</v>
       </c>
       <c r="B721" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -79015,7 +79015,7 @@
         <v>137238992</v>
       </c>
       <c r="B722" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -79121,7 +79121,7 @@
         <v>137239263</v>
       </c>
       <c r="B723" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -79227,7 +79227,7 @@
         <v>137239323</v>
       </c>
       <c r="B724" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -79333,7 +79333,7 @@
         <v>137240084</v>
       </c>
       <c r="B725" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -80340,7 +80340,7 @@
         <v>137239194</v>
       </c>
       <c r="B734" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>136801543</v>
       </c>
       <c r="B36" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>136824069</v>
       </c>
       <c r="B37" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>136842796</v>
       </c>
       <c r="B59" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>136842797</v>
       </c>
       <c r="B60" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>137045903</v>
       </c>
       <c r="B61" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045922</v>
       </c>
       <c r="B62" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137089183</v>
       </c>
       <c r="B63" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089291</v>
       </c>
       <c r="B64" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>136924180</v>
       </c>
       <c r="B69" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>136842798</v>
       </c>
       <c r="B72" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>137045913</v>
       </c>
       <c r="B73" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045925</v>
       </c>
       <c r="B74" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045932</v>
       </c>
       <c r="B75" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045939</v>
       </c>
       <c r="B76" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137089303</v>
       </c>
       <c r="B77" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089326</v>
       </c>
       <c r="B78" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089870</v>
       </c>
       <c r="B79" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137106221</v>
       </c>
       <c r="B80" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106272</v>
       </c>
       <c r="B81" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137144281</v>
       </c>
       <c r="B82" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144302</v>
       </c>
       <c r="B83" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>137045899</v>
       </c>
       <c r="B90" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>137090029</v>
       </c>
       <c r="B101" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090074</v>
       </c>
       <c r="B102" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137144342</v>
       </c>
       <c r="B103" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>137089891</v>
       </c>
       <c r="B106" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>136823635</v>
       </c>
       <c r="B109" t="n">
-        <v>90908</v>
+        <v>90913</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>136823659</v>
       </c>
       <c r="B110" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>136824686</v>
       </c>
       <c r="B111" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136843504</v>
       </c>
       <c r="B112" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12911,7 +12911,7 @@
         <v>136823526</v>
       </c>
       <c r="B115" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>136842628</v>
       </c>
       <c r="B117" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>136823927</v>
       </c>
       <c r="B128" t="n">
-        <v>90908</v>
+        <v>90913</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>136842963</v>
       </c>
       <c r="B129" t="n">
-        <v>90908</v>
+        <v>90913</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136941046</v>
       </c>
       <c r="B130" t="n">
-        <v>90908</v>
+        <v>90913</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>136824654</v>
       </c>
       <c r="B131" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>136842826</v>
       </c>
       <c r="B132" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>136842985</v>
       </c>
       <c r="B133" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>136843093</v>
       </c>
       <c r="B134" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>136843333</v>
       </c>
       <c r="B135" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>136823841</v>
       </c>
       <c r="B142" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>136823870</v>
       </c>
       <c r="B143" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>136823898</v>
       </c>
       <c r="B144" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>136823966</v>
       </c>
       <c r="B145" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>136823975</v>
       </c>
       <c r="B146" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>136824666</v>
       </c>
       <c r="B147" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>136842642</v>
       </c>
       <c r="B148" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>136842789</v>
       </c>
       <c r="B149" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>136842977</v>
       </c>
       <c r="B150" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>136843078</v>
       </c>
       <c r="B151" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>136843134</v>
       </c>
       <c r="B152" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>136842801</v>
       </c>
       <c r="B158" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>136842998</v>
       </c>
       <c r="B161" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>136823791</v>
       </c>
       <c r="B168" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>136823881</v>
       </c>
       <c r="B169" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>136824642</v>
       </c>
       <c r="B170" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>136824678</v>
       </c>
       <c r="B171" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>136842702</v>
       </c>
       <c r="B172" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136842790</v>
       </c>
       <c r="B173" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>136842972</v>
       </c>
       <c r="B174" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>136843073</v>
       </c>
       <c r="B175" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>136843129</v>
       </c>
       <c r="B176" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>136843227</v>
       </c>
       <c r="B177" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136843356</v>
       </c>
       <c r="B178" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>137107311</v>
       </c>
       <c r="B179" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>136823813</v>
       </c>
       <c r="B184" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137045906</v>
       </c>
       <c r="B193" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>136843399</v>
       </c>
       <c r="B194" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>137106293</v>
       </c>
       <c r="B195" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106421</v>
       </c>
       <c r="B196" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106491</v>
       </c>
       <c r="B197" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106521</v>
       </c>
       <c r="B198" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106571</v>
       </c>
       <c r="B199" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>137106348</v>
       </c>
       <c r="B210" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106366</v>
       </c>
       <c r="B211" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106378</v>
       </c>
       <c r="B212" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106442</v>
       </c>
       <c r="B213" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106474</v>
       </c>
       <c r="B214" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106502</v>
       </c>
       <c r="B215" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137144390</v>
       </c>
       <c r="B216" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144403</v>
       </c>
       <c r="B217" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144419</v>
       </c>
       <c r="B218" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144429</v>
       </c>
       <c r="B219" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>136843411</v>
       </c>
       <c r="B223" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>137144356</v>
       </c>
       <c r="B229" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25969,7 +25969,7 @@
         <v>137144374</v>
       </c>
       <c r="B236" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>137143190</v>
       </c>
       <c r="B254" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>137143205</v>
       </c>
       <c r="B255" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143230</v>
       </c>
       <c r="B256" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137144549</v>
       </c>
       <c r="B257" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>137143034</v>
       </c>
       <c r="B289" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>137124255</v>
       </c>
       <c r="B297" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>137142668</v>
       </c>
       <c r="B298" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137142944</v>
       </c>
       <c r="B299" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137143162</v>
       </c>
       <c r="B300" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>137143048</v>
       </c>
       <c r="B304" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>137142760</v>
       </c>
       <c r="B307" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>137142797</v>
       </c>
       <c r="B308" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>137107280</v>
       </c>
       <c r="B316" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>137124150</v>
       </c>
       <c r="B317" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137124193</v>
       </c>
       <c r="B318" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137142713</v>
       </c>
       <c r="B319" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137142721</v>
       </c>
       <c r="B320" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142731</v>
       </c>
       <c r="B321" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142818</v>
       </c>
       <c r="B322" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142840</v>
       </c>
       <c r="B323" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137143060</v>
       </c>
       <c r="B324" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137143076</v>
       </c>
       <c r="B325" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143137</v>
       </c>
       <c r="B326" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143177</v>
       </c>
       <c r="B327" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>137107090</v>
       </c>
       <c r="B348" t="n">
-        <v>90908</v>
+        <v>90913</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         <v>137106534</v>
       </c>
       <c r="B352" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>137106671</v>
       </c>
       <c r="B353" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137107185</v>
       </c>
       <c r="B354" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106597</v>
       </c>
       <c r="B355" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>137106552</v>
       </c>
       <c r="B361" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>137106662</v>
       </c>
       <c r="B362" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137107145</v>
       </c>
       <c r="B363" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137107170</v>
       </c>
       <c r="B364" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107199</v>
       </c>
       <c r="B365" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107238</v>
       </c>
       <c r="B366" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107267</v>
       </c>
       <c r="B367" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107297</v>
       </c>
       <c r="B368" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137142621</v>
       </c>
       <c r="B369" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>137016225</v>
       </c>
       <c r="B381" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>137016093</v>
       </c>
       <c r="B383" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>137016208</v>
       </c>
       <c r="B384" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016378</v>
       </c>
       <c r="B386" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>137016422</v>
       </c>
       <c r="B405" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>137123693</v>
       </c>
       <c r="B413" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -45237,7 +45237,7 @@
         <v>137143246</v>
       </c>
       <c r="B414" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -45343,7 +45343,7 @@
         <v>137144503</v>
       </c>
       <c r="B415" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137144527</v>
       </c>
       <c r="B416" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -46522,7 +46522,7 @@
         <v>137124073</v>
       </c>
       <c r="B426" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137123623</v>
       </c>
       <c r="B429" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -46946,7 +46946,7 @@
         <v>137123636</v>
       </c>
       <c r="B430" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -47052,7 +47052,7 @@
         <v>137123709</v>
       </c>
       <c r="B431" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123822</v>
       </c>
       <c r="B432" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123842</v>
       </c>
       <c r="B433" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123906</v>
       </c>
       <c r="B434" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137124052</v>
       </c>
       <c r="B435" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137290863</v>
       </c>
       <c r="B436" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137291615</v>
       </c>
       <c r="B437" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>137291623</v>
       </c>
       <c r="B438" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>137123759</v>
       </c>
       <c r="B445" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>137124010</v>
       </c>
       <c r="B446" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>137291594</v>
       </c>
       <c r="B460" t="n">
-        <v>93459</v>
+        <v>93465</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>137144483</v>
       </c>
       <c r="B461" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>137144492</v>
       </c>
       <c r="B462" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>137291563</v>
       </c>
       <c r="B463" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>137291571</v>
       </c>
       <c r="B464" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>137016352</v>
       </c>
       <c r="B506" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -55429,7 +55429,7 @@
         <v>137016265</v>
       </c>
       <c r="B507" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59657,7 +59657,7 @@
         <v>137290686</v>
       </c>
       <c r="B545" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -60316,7 +60316,7 @@
         <v>137291317</v>
       </c>
       <c r="B551" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -60754,7 +60754,7 @@
         <v>137291210</v>
       </c>
       <c r="B555" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>137290838</v>
       </c>
       <c r="B559" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -61288,7 +61288,7 @@
         <v>137290848</v>
       </c>
       <c r="B560" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>137290857</v>
       </c>
       <c r="B561" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>137291070</v>
       </c>
       <c r="B562" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>137291162</v>
       </c>
       <c r="B563" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>137291186</v>
       </c>
       <c r="B564" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>137291193</v>
       </c>
       <c r="B565" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>137291218</v>
       </c>
       <c r="B566" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>137291263</v>
       </c>
       <c r="B567" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -62141,7 +62141,7 @@
         <v>137291298</v>
       </c>
       <c r="B568" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>137291402</v>
       </c>
       <c r="B569" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -62353,7 +62353,7 @@
         <v>137291412</v>
       </c>
       <c r="B570" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>137291421</v>
       </c>
       <c r="B571" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>137291426</v>
       </c>
       <c r="B589" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>137291430</v>
       </c>
       <c r="B590" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -64667,7 +64667,7 @@
         <v>137291534</v>
       </c>
       <c r="B591" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>137291554</v>
       </c>
       <c r="B592" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -66274,7 +66274,7 @@
         <v>137238726</v>
       </c>
       <c r="B606" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -66732,7 +66732,7 @@
         <v>137240254</v>
       </c>
       <c r="B610" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -67527,7 +67527,7 @@
         <v>137290579</v>
       </c>
       <c r="B617" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -68223,7 +68223,7 @@
         <v>137290591</v>
       </c>
       <c r="B623" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>137290729</v>
       </c>
       <c r="B627" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -68753,7 +68753,7 @@
         <v>137290756</v>
       </c>
       <c r="B628" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>137290815</v>
       </c>
       <c r="B629" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -71386,7 +71386,7 @@
         <v>137240024</v>
       </c>
       <c r="B652" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -71492,7 +71492,7 @@
         <v>137240039</v>
       </c>
       <c r="B653" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -72369,7 +72369,7 @@
         <v>137238841</v>
       </c>
       <c r="B661" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -72475,7 +72475,7 @@
         <v>137238858</v>
       </c>
       <c r="B662" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -72581,7 +72581,7 @@
         <v>137240141</v>
       </c>
       <c r="B663" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -73038,7 +73038,7 @@
         <v>137240203</v>
       </c>
       <c r="B667" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -73260,7 +73260,7 @@
         <v>137238811</v>
       </c>
       <c r="B669" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -75438,7 +75438,7 @@
         <v>137239472</v>
       </c>
       <c r="B689" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -75544,7 +75544,7 @@
         <v>137239964</v>
       </c>
       <c r="B690" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -75650,7 +75650,7 @@
         <v>137240074</v>
       </c>
       <c r="B691" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>137239535</v>
       </c>
       <c r="B700" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -76742,7 +76742,7 @@
         <v>137239564</v>
       </c>
       <c r="B701" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -76848,7 +76848,7 @@
         <v>137239989</v>
       </c>
       <c r="B702" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -77730,7 +77730,7 @@
         <v>137239483</v>
       </c>
       <c r="B710" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -77836,7 +77836,7 @@
         <v>137239495</v>
       </c>
       <c r="B711" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -78485,7 +78485,7 @@
         <v>137240122</v>
       </c>
       <c r="B717" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -78803,7 +78803,7 @@
         <v>137238959</v>
       </c>
       <c r="B720" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -78909,7 +78909,7 @@
         <v>137238973</v>
       </c>
       <c r="B721" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -79015,7 +79015,7 @@
         <v>137238992</v>
       </c>
       <c r="B722" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -79121,7 +79121,7 @@
         <v>137239263</v>
       </c>
       <c r="B723" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -79227,7 +79227,7 @@
         <v>137239323</v>
       </c>
       <c r="B724" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -79333,7 +79333,7 @@
         <v>137240084</v>
       </c>
       <c r="B725" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -80234,7 +80234,7 @@
         <v>137239011</v>
       </c>
       <c r="B733" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -80340,7 +80340,7 @@
         <v>137239194</v>
       </c>
       <c r="B734" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>128679710</v>
       </c>
       <c r="B32" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         <v>136842796</v>
       </c>
       <c r="B60" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>136842797</v>
       </c>
       <c r="B61" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045903</v>
       </c>
       <c r="B62" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137045922</v>
       </c>
       <c r="B63" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089183</v>
       </c>
       <c r="B64" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>137089291</v>
       </c>
       <c r="B65" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>136924180</v>
       </c>
       <c r="B70" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>136842798</v>
       </c>
       <c r="B73" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045913</v>
       </c>
       <c r="B74" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045925</v>
       </c>
       <c r="B75" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045932</v>
       </c>
       <c r="B76" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137045939</v>
       </c>
       <c r="B77" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089303</v>
       </c>
       <c r="B78" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089326</v>
       </c>
       <c r="B79" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137089870</v>
       </c>
       <c r="B80" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106221</v>
       </c>
       <c r="B81" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137106272</v>
       </c>
       <c r="B82" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144281</v>
       </c>
       <c r="B83" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>137144302</v>
       </c>
       <c r="B84" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090029</v>
       </c>
       <c r="B102" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137090074</v>
       </c>
       <c r="B103" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>137144342</v>
       </c>
       <c r="B104" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>137089891</v>
       </c>
       <c r="B107" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>136843504</v>
       </c>
       <c r="B113" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>136842963</v>
       </c>
       <c r="B130" t="n">
-        <v>90913</v>
+        <v>90924</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>136941046</v>
       </c>
       <c r="B131" t="n">
-        <v>90913</v>
+        <v>90924</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>136842826</v>
       </c>
       <c r="B133" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>136842985</v>
       </c>
       <c r="B134" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>136843093</v>
       </c>
       <c r="B135" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>136843333</v>
       </c>
       <c r="B136" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>136842642</v>
       </c>
       <c r="B149" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>136842789</v>
       </c>
       <c r="B150" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>136842977</v>
       </c>
       <c r="B151" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>136843078</v>
       </c>
       <c r="B152" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>136843134</v>
       </c>
       <c r="B153" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>136842801</v>
       </c>
       <c r="B159" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>136842998</v>
       </c>
       <c r="B162" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>136842702</v>
       </c>
       <c r="B173" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>136842790</v>
       </c>
       <c r="B174" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>136842972</v>
       </c>
       <c r="B175" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>136843073</v>
       </c>
       <c r="B176" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>136843129</v>
       </c>
       <c r="B177" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>136843227</v>
       </c>
       <c r="B178" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>136843356</v>
       </c>
       <c r="B179" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>137107311</v>
       </c>
       <c r="B180" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>137045906</v>
       </c>
       <c r="B194" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>136843399</v>
       </c>
       <c r="B195" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106293</v>
       </c>
       <c r="B196" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106421</v>
       </c>
       <c r="B197" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106491</v>
       </c>
       <c r="B198" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106521</v>
       </c>
       <c r="B199" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>137106571</v>
       </c>
       <c r="B200" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106348</v>
       </c>
       <c r="B211" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106366</v>
       </c>
       <c r="B212" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106378</v>
       </c>
       <c r="B213" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106442</v>
       </c>
       <c r="B214" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106474</v>
       </c>
       <c r="B215" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137106502</v>
       </c>
       <c r="B216" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144390</v>
       </c>
       <c r="B217" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144403</v>
       </c>
       <c r="B218" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144419</v>
       </c>
       <c r="B219" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>137144429</v>
       </c>
       <c r="B220" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>136843411</v>
       </c>
       <c r="B224" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>112077997</v>
       </c>
       <c r="B233" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>137144374</v>
       </c>
       <c r="B238" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143190</v>
       </c>
       <c r="B256" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137143205</v>
       </c>
       <c r="B257" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>137143230</v>
       </c>
       <c r="B258" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>137144549</v>
       </c>
       <c r="B259" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>137143034</v>
       </c>
       <c r="B291" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137124255</v>
       </c>
       <c r="B299" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137142668</v>
       </c>
       <c r="B300" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>137142944</v>
       </c>
       <c r="B301" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>137143162</v>
       </c>
       <c r="B302" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>137143048</v>
       </c>
       <c r="B306" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>137142760</v>
       </c>
       <c r="B309" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>137142797</v>
       </c>
       <c r="B310" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137107280</v>
       </c>
       <c r="B318" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137124150</v>
       </c>
       <c r="B319" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137124193</v>
       </c>
       <c r="B320" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142713</v>
       </c>
       <c r="B321" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142721</v>
       </c>
       <c r="B322" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142731</v>
       </c>
       <c r="B323" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137142818</v>
       </c>
       <c r="B324" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137142840</v>
       </c>
       <c r="B325" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143060</v>
       </c>
       <c r="B326" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143076</v>
       </c>
       <c r="B327" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>137143137</v>
       </c>
       <c r="B328" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>137143177</v>
       </c>
       <c r="B329" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>137107090</v>
       </c>
       <c r="B350" t="n">
-        <v>90913</v>
+        <v>90924</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137106534</v>
       </c>
       <c r="B354" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106671</v>
       </c>
       <c r="B355" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>137107185</v>
       </c>
       <c r="B356" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>137106597</v>
       </c>
       <c r="B357" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137106552</v>
       </c>
       <c r="B363" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137106662</v>
       </c>
       <c r="B364" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107145</v>
       </c>
       <c r="B365" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107170</v>
       </c>
       <c r="B366" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107199</v>
       </c>
       <c r="B367" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107238</v>
       </c>
       <c r="B368" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137107267</v>
       </c>
       <c r="B369" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>137107297</v>
       </c>
       <c r="B370" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>137142621</v>
       </c>
       <c r="B371" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>137016225</v>
       </c>
       <c r="B383" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>137016093</v>
       </c>
       <c r="B385" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016208</v>
       </c>
       <c r="B386" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>137016378</v>
       </c>
       <c r="B388" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>112561944</v>
       </c>
       <c r="B394" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>137016422</v>
       </c>
       <c r="B408" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137123693</v>
       </c>
       <c r="B416" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>137143246</v>
       </c>
       <c r="B417" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>137144503</v>
       </c>
       <c r="B418" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>137144527</v>
       </c>
       <c r="B419" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137124073</v>
       </c>
       <c r="B429" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123623</v>
       </c>
       <c r="B432" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123636</v>
       </c>
       <c r="B433" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123709</v>
       </c>
       <c r="B434" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137123822</v>
       </c>
       <c r="B435" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137123842</v>
       </c>
       <c r="B436" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137123906</v>
       </c>
       <c r="B437" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>137124052</v>
       </c>
       <c r="B438" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>137290863</v>
       </c>
       <c r="B439" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>137291615</v>
       </c>
       <c r="B440" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>137291623</v>
       </c>
       <c r="B441" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>137291594</v>
       </c>
       <c r="B463" t="n">
-        <v>93465</v>
+        <v>93477</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>137144483</v>
       </c>
       <c r="B464" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>137144492</v>
       </c>
       <c r="B465" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>137291563</v>
       </c>
       <c r="B466" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>137291571</v>
       </c>
       <c r="B467" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>137016352</v>
       </c>
       <c r="B509" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>137016265</v>
       </c>
       <c r="B510" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>137290686</v>
       </c>
       <c r="B548" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>137291317</v>
       </c>
       <c r="B554" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>137291210</v>
       </c>
       <c r="B558" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>137290838</v>
       </c>
       <c r="B562" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>137290848</v>
       </c>
       <c r="B563" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>137290857</v>
       </c>
       <c r="B564" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>137291070</v>
       </c>
       <c r="B565" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>137291162</v>
       </c>
       <c r="B566" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>137291186</v>
       </c>
       <c r="B567" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>137291193</v>
       </c>
       <c r="B568" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>137291218</v>
       </c>
       <c r="B569" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -62348,7 +62348,7 @@
         <v>137291263</v>
       </c>
       <c r="B570" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>137291298</v>
       </c>
       <c r="B571" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -62565,7 +62565,7 @@
         <v>137291402</v>
       </c>
       <c r="B572" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         <v>137291412</v>
       </c>
       <c r="B573" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -62777,7 +62777,7 @@
         <v>137291421</v>
       </c>
       <c r="B574" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>137291426</v>
       </c>
       <c r="B592" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>137291430</v>
       </c>
       <c r="B593" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -64985,7 +64985,7 @@
         <v>137291534</v>
       </c>
       <c r="B594" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>137291554</v>
       </c>
       <c r="B595" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -66592,7 +66592,7 @@
         <v>137238726</v>
       </c>
       <c r="B609" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>137290579</v>
       </c>
       <c r="B620" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>137290591</v>
       </c>
       <c r="B626" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -68965,7 +68965,7 @@
         <v>137290729</v>
       </c>
       <c r="B630" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>137290756</v>
       </c>
       <c r="B631" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>137240024</v>
       </c>
       <c r="B655" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -71810,7 +71810,7 @@
         <v>137240039</v>
       </c>
       <c r="B656" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -72687,7 +72687,7 @@
         <v>137238841</v>
       </c>
       <c r="B664" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -72793,7 +72793,7 @@
         <v>137238858</v>
       </c>
       <c r="B665" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -72899,7 +72899,7 @@
         <v>137240141</v>
       </c>
       <c r="B666" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -73356,7 +73356,7 @@
         <v>137240203</v>
       </c>
       <c r="B670" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>137238811</v>
       </c>
       <c r="B672" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -75756,7 +75756,7 @@
         <v>137239472</v>
       </c>
       <c r="B692" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -75862,7 +75862,7 @@
         <v>137239964</v>
       </c>
       <c r="B693" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -75968,7 +75968,7 @@
         <v>137240074</v>
       </c>
       <c r="B694" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -76954,7 +76954,7 @@
         <v>137239535</v>
       </c>
       <c r="B703" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -77060,7 +77060,7 @@
         <v>137239564</v>
       </c>
       <c r="B704" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -77166,7 +77166,7 @@
         <v>137239989</v>
       </c>
       <c r="B705" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>128625864</v>
       </c>
       <c r="B716" t="n">
-        <v>93490</v>
+        <v>93502</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -78909,7 +78909,7 @@
         <v>137240122</v>
       </c>
       <c r="B721" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -79227,7 +79227,7 @@
         <v>137238959</v>
       </c>
       <c r="B724" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -79333,7 +79333,7 @@
         <v>137238973</v>
       </c>
       <c r="B725" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -79439,7 +79439,7 @@
         <v>137238992</v>
       </c>
       <c r="B726" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -79545,7 +79545,7 @@
         <v>137239263</v>
       </c>
       <c r="B727" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>137239323</v>
       </c>
       <c r="B728" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -79757,7 +79757,7 @@
         <v>137240084</v>
       </c>
       <c r="B729" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -80764,7 +80764,7 @@
         <v>137239194</v>
       </c>
       <c r="B738" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>128679710</v>
       </c>
       <c r="B32" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045903</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137045922</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089183</v>
       </c>
       <c r="B64" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>137089291</v>
       </c>
       <c r="B65" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>136924180</v>
       </c>
       <c r="B70" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045913</v>
       </c>
       <c r="B74" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045925</v>
       </c>
       <c r="B75" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045932</v>
       </c>
       <c r="B76" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137045939</v>
       </c>
       <c r="B77" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089303</v>
       </c>
       <c r="B78" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089326</v>
       </c>
       <c r="B79" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137089870</v>
       </c>
       <c r="B80" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106221</v>
       </c>
       <c r="B81" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137106272</v>
       </c>
       <c r="B82" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144281</v>
       </c>
       <c r="B83" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>137144302</v>
       </c>
       <c r="B84" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090029</v>
       </c>
       <c r="B102" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137090074</v>
       </c>
       <c r="B103" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>137144342</v>
       </c>
       <c r="B104" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>137089891</v>
       </c>
       <c r="B107" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>136941046</v>
       </c>
       <c r="B131" t="n">
-        <v>90924</v>
+        <v>90925</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>137107311</v>
       </c>
       <c r="B180" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>137045906</v>
       </c>
       <c r="B194" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106293</v>
       </c>
       <c r="B196" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106421</v>
       </c>
       <c r="B197" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106491</v>
       </c>
       <c r="B198" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106521</v>
       </c>
       <c r="B199" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>137106571</v>
       </c>
       <c r="B200" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106348</v>
       </c>
       <c r="B211" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106366</v>
       </c>
       <c r="B212" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106378</v>
       </c>
       <c r="B213" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106442</v>
       </c>
       <c r="B214" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106474</v>
       </c>
       <c r="B215" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137106502</v>
       </c>
       <c r="B216" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144390</v>
       </c>
       <c r="B217" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144403</v>
       </c>
       <c r="B218" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144419</v>
       </c>
       <c r="B219" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>137144429</v>
       </c>
       <c r="B220" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>112077997</v>
       </c>
       <c r="B233" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>137144374</v>
       </c>
       <c r="B238" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143190</v>
       </c>
       <c r="B256" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137143205</v>
       </c>
       <c r="B257" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>137143230</v>
       </c>
       <c r="B258" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>137144549</v>
       </c>
       <c r="B259" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>137143034</v>
       </c>
       <c r="B291" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137124255</v>
       </c>
       <c r="B299" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137142668</v>
       </c>
       <c r="B300" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>137142944</v>
       </c>
       <c r="B301" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>137143162</v>
       </c>
       <c r="B302" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>137143048</v>
       </c>
       <c r="B306" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>137142760</v>
       </c>
       <c r="B309" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>137142797</v>
       </c>
       <c r="B310" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137107280</v>
       </c>
       <c r="B318" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137124150</v>
       </c>
       <c r="B319" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137124193</v>
       </c>
       <c r="B320" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142713</v>
       </c>
       <c r="B321" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142721</v>
       </c>
       <c r="B322" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142731</v>
       </c>
       <c r="B323" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137142818</v>
       </c>
       <c r="B324" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137142840</v>
       </c>
       <c r="B325" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143060</v>
       </c>
       <c r="B326" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143076</v>
       </c>
       <c r="B327" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>137143137</v>
       </c>
       <c r="B328" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>137143177</v>
       </c>
       <c r="B329" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>137107090</v>
       </c>
       <c r="B350" t="n">
-        <v>90924</v>
+        <v>90925</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137106534</v>
       </c>
       <c r="B354" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106671</v>
       </c>
       <c r="B355" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>137107185</v>
       </c>
       <c r="B356" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>137106597</v>
       </c>
       <c r="B357" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137106552</v>
       </c>
       <c r="B363" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137106662</v>
       </c>
       <c r="B364" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107145</v>
       </c>
       <c r="B365" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107170</v>
       </c>
       <c r="B366" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107199</v>
       </c>
       <c r="B367" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107238</v>
       </c>
       <c r="B368" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137107267</v>
       </c>
       <c r="B369" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>137107297</v>
       </c>
       <c r="B370" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>137142621</v>
       </c>
       <c r="B371" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>137016225</v>
       </c>
       <c r="B383" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>137016093</v>
       </c>
       <c r="B385" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016208</v>
       </c>
       <c r="B386" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>137016378</v>
       </c>
       <c r="B388" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>112561944</v>
       </c>
       <c r="B394" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>137016422</v>
       </c>
       <c r="B408" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137123693</v>
       </c>
       <c r="B416" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>137143246</v>
       </c>
       <c r="B417" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>137144503</v>
       </c>
       <c r="B418" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>137144527</v>
       </c>
       <c r="B419" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137124073</v>
       </c>
       <c r="B429" t="n">
-        <v>93475</v>
+        <v>93476</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123623</v>
       </c>
       <c r="B432" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123636</v>
       </c>
       <c r="B433" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123709</v>
       </c>
       <c r="B434" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137123822</v>
       </c>
       <c r="B435" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137123842</v>
       </c>
       <c r="B436" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137123906</v>
       </c>
       <c r="B437" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>137124052</v>
       </c>
       <c r="B438" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>137290863</v>
       </c>
       <c r="B439" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>137291615</v>
       </c>
       <c r="B440" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>137291623</v>
       </c>
       <c r="B441" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>137291594</v>
       </c>
       <c r="B463" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>137144483</v>
       </c>
       <c r="B464" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>137144492</v>
       </c>
       <c r="B465" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>137291563</v>
       </c>
       <c r="B466" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>137291571</v>
       </c>
       <c r="B467" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>137016352</v>
       </c>
       <c r="B509" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>137016265</v>
       </c>
       <c r="B510" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>137290686</v>
       </c>
       <c r="B548" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>137291317</v>
       </c>
       <c r="B554" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>137291210</v>
       </c>
       <c r="B558" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>137290838</v>
       </c>
       <c r="B562" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>137290848</v>
       </c>
       <c r="B563" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>137290857</v>
       </c>
       <c r="B564" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>137291070</v>
       </c>
       <c r="B565" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>137291162</v>
       </c>
       <c r="B566" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>137291186</v>
       </c>
       <c r="B567" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>137291193</v>
       </c>
       <c r="B568" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>137291218</v>
       </c>
       <c r="B569" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -62348,7 +62348,7 @@
         <v>137291263</v>
       </c>
       <c r="B570" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>137291298</v>
       </c>
       <c r="B571" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -62565,7 +62565,7 @@
         <v>137291402</v>
       </c>
       <c r="B572" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         <v>137291412</v>
       </c>
       <c r="B573" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -62777,7 +62777,7 @@
         <v>137291421</v>
       </c>
       <c r="B574" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>137291426</v>
       </c>
       <c r="B592" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>137291430</v>
       </c>
       <c r="B593" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -64985,7 +64985,7 @@
         <v>137291534</v>
       </c>
       <c r="B594" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>137291554</v>
       </c>
       <c r="B595" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -66592,7 +66592,7 @@
         <v>137238726</v>
       </c>
       <c r="B609" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>137290579</v>
       </c>
       <c r="B620" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>137290591</v>
       </c>
       <c r="B626" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -68965,7 +68965,7 @@
         <v>137290729</v>
       </c>
       <c r="B630" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>137290756</v>
       </c>
       <c r="B631" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>137240024</v>
       </c>
       <c r="B655" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -71810,7 +71810,7 @@
         <v>137240039</v>
       </c>
       <c r="B656" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -72687,7 +72687,7 @@
         <v>137238841</v>
       </c>
       <c r="B664" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -72793,7 +72793,7 @@
         <v>137238858</v>
       </c>
       <c r="B665" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -72899,7 +72899,7 @@
         <v>137240141</v>
       </c>
       <c r="B666" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -73356,7 +73356,7 @@
         <v>137240203</v>
       </c>
       <c r="B670" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>137238811</v>
       </c>
       <c r="B672" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -75756,7 +75756,7 @@
         <v>137239472</v>
       </c>
       <c r="B692" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -75862,7 +75862,7 @@
         <v>137239964</v>
       </c>
       <c r="B693" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -75968,7 +75968,7 @@
         <v>137240074</v>
       </c>
       <c r="B694" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -76954,7 +76954,7 @@
         <v>137239535</v>
       </c>
       <c r="B703" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -77060,7 +77060,7 @@
         <v>137239564</v>
       </c>
       <c r="B704" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -77166,7 +77166,7 @@
         <v>137239989</v>
       </c>
       <c r="B705" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>128625864</v>
       </c>
       <c r="B716" t="n">
-        <v>93502</v>
+        <v>93503</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -78909,7 +78909,7 @@
         <v>137240122</v>
       </c>
       <c r="B721" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -79227,7 +79227,7 @@
         <v>137238959</v>
       </c>
       <c r="B724" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -79333,7 +79333,7 @@
         <v>137238973</v>
       </c>
       <c r="B725" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -79439,7 +79439,7 @@
         <v>137238992</v>
       </c>
       <c r="B726" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -79545,7 +79545,7 @@
         <v>137239263</v>
       </c>
       <c r="B727" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>137239323</v>
       </c>
       <c r="B728" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -79757,7 +79757,7 @@
         <v>137240084</v>
       </c>
       <c r="B729" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -80764,7 +80764,7 @@
         <v>137239194</v>
       </c>
       <c r="B738" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>128679710</v>
       </c>
       <c r="B32" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045903</v>
       </c>
       <c r="B62" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137045922</v>
       </c>
       <c r="B63" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089183</v>
       </c>
       <c r="B64" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>137089291</v>
       </c>
       <c r="B65" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>136924180</v>
       </c>
       <c r="B70" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045913</v>
       </c>
       <c r="B74" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045925</v>
       </c>
       <c r="B75" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045932</v>
       </c>
       <c r="B76" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137045939</v>
       </c>
       <c r="B77" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089303</v>
       </c>
       <c r="B78" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089326</v>
       </c>
       <c r="B79" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137089870</v>
       </c>
       <c r="B80" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106221</v>
       </c>
       <c r="B81" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137106272</v>
       </c>
       <c r="B82" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144281</v>
       </c>
       <c r="B83" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>137144302</v>
       </c>
       <c r="B84" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090029</v>
       </c>
       <c r="B102" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137090074</v>
       </c>
       <c r="B103" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>137144342</v>
       </c>
       <c r="B104" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>137089891</v>
       </c>
       <c r="B107" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>136941046</v>
       </c>
       <c r="B131" t="n">
-        <v>90925</v>
+        <v>90928</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>137107311</v>
       </c>
       <c r="B180" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>137045906</v>
       </c>
       <c r="B194" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106293</v>
       </c>
       <c r="B196" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106421</v>
       </c>
       <c r="B197" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106491</v>
       </c>
       <c r="B198" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106521</v>
       </c>
       <c r="B199" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>137106571</v>
       </c>
       <c r="B200" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106348</v>
       </c>
       <c r="B211" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106366</v>
       </c>
       <c r="B212" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106378</v>
       </c>
       <c r="B213" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106442</v>
       </c>
       <c r="B214" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106474</v>
       </c>
       <c r="B215" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137106502</v>
       </c>
       <c r="B216" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144390</v>
       </c>
       <c r="B217" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144403</v>
       </c>
       <c r="B218" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144419</v>
       </c>
       <c r="B219" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>137144429</v>
       </c>
       <c r="B220" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>112077997</v>
       </c>
       <c r="B233" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>137144374</v>
       </c>
       <c r="B238" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>137143190</v>
       </c>
       <c r="B256" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>137143205</v>
       </c>
       <c r="B257" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>137143230</v>
       </c>
       <c r="B258" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>137144549</v>
       </c>
       <c r="B259" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>137143034</v>
       </c>
       <c r="B291" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>137124255</v>
       </c>
       <c r="B299" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>137142668</v>
       </c>
       <c r="B300" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>137142944</v>
       </c>
       <c r="B301" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>137143162</v>
       </c>
       <c r="B302" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>137143048</v>
       </c>
       <c r="B306" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>137142760</v>
       </c>
       <c r="B309" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -33969,7 +33969,7 @@
         <v>137142797</v>
       </c>
       <c r="B310" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>137107280</v>
       </c>
       <c r="B318" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -34928,7 +34928,7 @@
         <v>137124150</v>
       </c>
       <c r="B319" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>137124193</v>
       </c>
       <c r="B320" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>137142713</v>
       </c>
       <c r="B321" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>137142721</v>
       </c>
       <c r="B322" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>137142731</v>
       </c>
       <c r="B323" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>137142818</v>
       </c>
       <c r="B324" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>137142840</v>
       </c>
       <c r="B325" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>137143060</v>
       </c>
       <c r="B326" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>137143076</v>
       </c>
       <c r="B327" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>137143137</v>
       </c>
       <c r="B328" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>137143177</v>
       </c>
       <c r="B329" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -38273,7 +38273,7 @@
         <v>137107090</v>
       </c>
       <c r="B350" t="n">
-        <v>90925</v>
+        <v>90928</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>137106534</v>
       </c>
       <c r="B354" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>137106671</v>
       </c>
       <c r="B355" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>137107185</v>
       </c>
       <c r="B356" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -39015,7 +39015,7 @@
         <v>137106597</v>
       </c>
       <c r="B357" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>137106552</v>
       </c>
       <c r="B363" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -39771,7 +39771,7 @@
         <v>137106662</v>
       </c>
       <c r="B364" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>137107145</v>
       </c>
       <c r="B365" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>137107170</v>
       </c>
       <c r="B366" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>137107199</v>
       </c>
       <c r="B367" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40195,7 +40195,7 @@
         <v>137107238</v>
       </c>
       <c r="B368" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>137107267</v>
       </c>
       <c r="B369" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>137107297</v>
       </c>
       <c r="B370" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -40513,7 +40513,7 @@
         <v>137142621</v>
       </c>
       <c r="B371" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>137016225</v>
       </c>
       <c r="B383" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -42047,7 +42047,7 @@
         <v>137016093</v>
       </c>
       <c r="B385" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -42153,7 +42153,7 @@
         <v>137016208</v>
       </c>
       <c r="B386" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>137016378</v>
       </c>
       <c r="B388" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>112561944</v>
       </c>
       <c r="B394" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>137016422</v>
       </c>
       <c r="B408" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -45449,7 +45449,7 @@
         <v>137123693</v>
       </c>
       <c r="B416" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>137143246</v>
       </c>
       <c r="B417" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>137144503</v>
       </c>
       <c r="B418" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>137144527</v>
       </c>
       <c r="B419" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>137124073</v>
       </c>
       <c r="B429" t="n">
-        <v>93476</v>
+        <v>93479</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>137123623</v>
       </c>
       <c r="B432" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -47264,7 +47264,7 @@
         <v>137123636</v>
       </c>
       <c r="B433" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>137123709</v>
       </c>
       <c r="B434" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>137123822</v>
       </c>
       <c r="B435" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>137123842</v>
       </c>
       <c r="B436" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>137123906</v>
       </c>
       <c r="B437" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -47794,7 +47794,7 @@
         <v>137124052</v>
       </c>
       <c r="B438" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>137290863</v>
       </c>
       <c r="B439" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -48006,7 +48006,7 @@
         <v>137291615</v>
       </c>
       <c r="B440" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -48112,7 +48112,7 @@
         <v>137291623</v>
       </c>
       <c r="B441" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -50608,7 +50608,7 @@
         <v>137291594</v>
       </c>
       <c r="B463" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -50714,7 +50714,7 @@
         <v>137144483</v>
       </c>
       <c r="B464" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>137144492</v>
       </c>
       <c r="B465" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>137291563</v>
       </c>
       <c r="B466" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -51032,7 +51032,7 @@
         <v>137291571</v>
       </c>
       <c r="B467" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -55641,7 +55641,7 @@
         <v>137016352</v>
       </c>
       <c r="B509" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>137016265</v>
       </c>
       <c r="B510" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>137290686</v>
       </c>
       <c r="B548" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -60634,7 +60634,7 @@
         <v>137291317</v>
       </c>
       <c r="B554" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -61072,7 +61072,7 @@
         <v>137291210</v>
       </c>
       <c r="B558" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -61500,7 +61500,7 @@
         <v>137290838</v>
       </c>
       <c r="B562" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>137290848</v>
       </c>
       <c r="B563" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -61712,7 +61712,7 @@
         <v>137290857</v>
       </c>
       <c r="B564" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -61818,7 +61818,7 @@
         <v>137291070</v>
       </c>
       <c r="B565" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>137291162</v>
       </c>
       <c r="B566" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -62030,7 +62030,7 @@
         <v>137291186</v>
       </c>
       <c r="B567" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -62136,7 +62136,7 @@
         <v>137291193</v>
       </c>
       <c r="B568" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>137291218</v>
       </c>
       <c r="B569" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -62348,7 +62348,7 @@
         <v>137291263</v>
       </c>
       <c r="B570" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>137291298</v>
       </c>
       <c r="B571" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -62565,7 +62565,7 @@
         <v>137291402</v>
       </c>
       <c r="B572" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         <v>137291412</v>
       </c>
       <c r="B573" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -62777,7 +62777,7 @@
         <v>137291421</v>
       </c>
       <c r="B574" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>137291426</v>
       </c>
       <c r="B592" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -64879,7 +64879,7 @@
         <v>137291430</v>
       </c>
       <c r="B593" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -64985,7 +64985,7 @@
         <v>137291534</v>
       </c>
       <c r="B594" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>137291554</v>
       </c>
       <c r="B595" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -66592,7 +66592,7 @@
         <v>137238726</v>
       </c>
       <c r="B609" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -67845,7 +67845,7 @@
         <v>137290579</v>
       </c>
       <c r="B620" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -68541,7 +68541,7 @@
         <v>137290591</v>
       </c>
       <c r="B626" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -68965,7 +68965,7 @@
         <v>137290729</v>
       </c>
       <c r="B630" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -69071,7 +69071,7 @@
         <v>137290756</v>
       </c>
       <c r="B631" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         <v>137240024</v>
       </c>
       <c r="B655" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -71810,7 +71810,7 @@
         <v>137240039</v>
       </c>
       <c r="B656" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -72687,7 +72687,7 @@
         <v>137238841</v>
       </c>
       <c r="B664" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -72793,7 +72793,7 @@
         <v>137238858</v>
       </c>
       <c r="B665" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -72899,7 +72899,7 @@
         <v>137240141</v>
       </c>
       <c r="B666" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -73356,7 +73356,7 @@
         <v>137240203</v>
       </c>
       <c r="B670" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -73578,7 +73578,7 @@
         <v>137238811</v>
       </c>
       <c r="B672" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -75756,7 +75756,7 @@
         <v>137239472</v>
       </c>
       <c r="B692" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -75862,7 +75862,7 @@
         <v>137239964</v>
       </c>
       <c r="B693" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -75968,7 +75968,7 @@
         <v>137240074</v>
       </c>
       <c r="B694" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -76954,7 +76954,7 @@
         <v>137239535</v>
       </c>
       <c r="B703" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -77060,7 +77060,7 @@
         <v>137239564</v>
       </c>
       <c r="B704" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -77166,7 +77166,7 @@
         <v>137239989</v>
       </c>
       <c r="B705" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -78375,7 +78375,7 @@
         <v>128625864</v>
       </c>
       <c r="B716" t="n">
-        <v>93503</v>
+        <v>93506</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -78909,7 +78909,7 @@
         <v>137240122</v>
       </c>
       <c r="B721" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -79227,7 +79227,7 @@
         <v>137238959</v>
       </c>
       <c r="B724" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -79333,7 +79333,7 @@
         <v>137238973</v>
       </c>
       <c r="B725" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -79439,7 +79439,7 @@
         <v>137238992</v>
       </c>
       <c r="B726" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -79545,7 +79545,7 @@
         <v>137239263</v>
       </c>
       <c r="B727" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -79651,7 +79651,7 @@
         <v>137239323</v>
       </c>
       <c r="B728" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -79757,7 +79757,7 @@
         <v>137240084</v>
       </c>
       <c r="B729" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -80764,7 +80764,7 @@
         <v>137239194</v>
       </c>
       <c r="B738" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -2439,7 +2439,7 @@
         <v>137090101</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>137090087</v>
       </c>
       <c r="B22" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137090125</v>
       </c>
       <c r="B23" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>128679710</v>
       </c>
       <c r="B32" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>137045903</v>
       </c>
       <c r="B62" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>137045922</v>
       </c>
       <c r="B63" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>137089183</v>
       </c>
       <c r="B64" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>137089291</v>
       </c>
       <c r="B65" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>137045913</v>
       </c>
       <c r="B74" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8571,7 +8571,7 @@
         <v>137045925</v>
       </c>
       <c r="B75" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137045932</v>
       </c>
       <c r="B76" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>137045939</v>
       </c>
       <c r="B77" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>137089303</v>
       </c>
       <c r="B78" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>137089326</v>
       </c>
       <c r="B79" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>137089870</v>
       </c>
       <c r="B80" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>137106221</v>
       </c>
       <c r="B81" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>137106272</v>
       </c>
       <c r="B82" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>137144281</v>
       </c>
       <c r="B83" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>137144302</v>
       </c>
       <c r="B84" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>137045899</v>
       </c>
       <c r="B91" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>137090029</v>
       </c>
       <c r="B102" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>137090074</v>
       </c>
       <c r="B103" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>137144342</v>
       </c>
       <c r="B104" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>137089891</v>
       </c>
       <c r="B107" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>136941046</v>
       </c>
       <c r="B131" t="n">
-        <v>90929</v>
+        <v>90932</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>137107311</v>
       </c>
       <c r="B180" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>137045906</v>
       </c>
       <c r="B194" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>137106293</v>
       </c>
       <c r="B196" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>137106421</v>
       </c>
       <c r="B197" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>137106491</v>
       </c>
       <c r="B198" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>137106521</v>
       </c>
       <c r="B199" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>137106571</v>
       </c>
       <c r="B200" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>137106348</v>
       </c>
       <c r="B211" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>137106366</v>
       </c>
       <c r="B212" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>137106378</v>
       </c>
       <c r="B213" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>137106442</v>
       </c>
       <c r="B214" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>137106474</v>
       </c>
       <c r="B215" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>137106502</v>
       </c>
       <c r="B216" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>137144390</v>
       </c>
       <c r="B217" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>137144403</v>
       </c>
       <c r="B218" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>137144419</v>
       </c>
       <c r="B219" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>137144429</v>
       </c>
       <c r="B220" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>137144356</v>
       </c>
       <c r="B230" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>112077997</v>
       </c>
       <c r="B233" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>137144374</v>
       </c>
       <c r="B238" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>137519065</v>
       </c>
       <c r="B244" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>137143190</v>
       </c>
       <c r="B257" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
         <v>137143205</v>
       </c>
       <c r="B258" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>137143230</v>
       </c>
       <c r="B259" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>137144549</v>
       </c>
       <c r="B260" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         <v>137143034</v>
       </c>
       <c r="B292" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>137124255</v>
       </c>
       <c r="B300" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>137142668</v>
       </c>
       <c r="B301" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>137142944</v>
       </c>
       <c r="B302" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -33216,7 +33216,7 @@
         <v>137143162</v>
       </c>
       <c r="B303" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>137143048</v>
       </c>
       <c r="B307" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>137142760</v>
       </c>
       <c r="B310" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>137142797</v>
       </c>
       <c r="B311" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>137107280</v>
       </c>
       <c r="B319" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>137124150</v>
       </c>
       <c r="B320" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         <v>137124193</v>
       </c>
       <c r="B321" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -35250,7 +35250,7 @@
         <v>137142713</v>
       </c>
       <c r="B322" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>137142721</v>
       </c>
       <c r="B323" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>137142731</v>
       </c>
       <c r="B324" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>137142818</v>
       </c>
       <c r="B325" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>137142840</v>
       </c>
       <c r="B326" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         <v>137143060</v>
       </c>
       <c r="B327" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>137143076</v>
       </c>
       <c r="B328" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>137143137</v>
       </c>
       <c r="B329" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>137143177</v>
       </c>
       <c r="B330" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>137107090</v>
       </c>
       <c r="B351" t="n">
-        <v>90928</v>
+        <v>90932</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>137106534</v>
       </c>
       <c r="B355" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>137106671</v>
       </c>
       <c r="B356" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>137107185</v>
       </c>
       <c r="B357" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -39125,7 +39125,7 @@
         <v>137106597</v>
       </c>
       <c r="B358" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>137106552</v>
       </c>
       <c r="B364" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -39881,7 +39881,7 @@
         <v>137106662</v>
       </c>
       <c r="B365" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>137107145</v>
       </c>
       <c r="B366" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>137107170</v>
       </c>
       <c r="B367" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>137107199</v>
       </c>
       <c r="B368" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>137107238</v>
       </c>
       <c r="B369" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>137107267</v>
       </c>
       <c r="B370" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>137107297</v>
       </c>
       <c r="B371" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -40623,7 +40623,7 @@
         <v>137142621</v>
       </c>
       <c r="B372" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>137016225</v>
       </c>
       <c r="B384" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>137519327</v>
       </c>
       <c r="B385" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>137016093</v>
       </c>
       <c r="B387" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>137016208</v>
       </c>
       <c r="B388" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>137016378</v>
       </c>
       <c r="B390" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>112561944</v>
       </c>
       <c r="B396" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>137519641</v>
       </c>
       <c r="B408" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>137016422</v>
       </c>
       <c r="B411" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -45022,7 +45022,7 @@
         <v>137519664</v>
       </c>
       <c r="B412" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>137123693</v>
       </c>
       <c r="B420" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>137143246</v>
       </c>
       <c r="B421" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>137144503</v>
       </c>
       <c r="B422" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>137144527</v>
       </c>
       <c r="B423" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>137124073</v>
       </c>
       <c r="B433" t="n">
-        <v>93479</v>
+        <v>93483</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -47586,7 +47586,7 @@
         <v>137123623</v>
       </c>
       <c r="B436" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>137123636</v>
       </c>
       <c r="B437" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>137123709</v>
       </c>
       <c r="B438" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>137123822</v>
       </c>
       <c r="B439" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>137123842</v>
       </c>
       <c r="B440" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>137123906</v>
       </c>
       <c r="B441" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>137124052</v>
       </c>
       <c r="B442" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -48328,7 +48328,7 @@
         <v>137290863</v>
       </c>
       <c r="B443" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>137291615</v>
       </c>
       <c r="B444" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -48540,7 +48540,7 @@
         <v>137291623</v>
       </c>
       <c r="B445" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>137123759</v>
       </c>
       <c r="B452" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -49421,7 +49421,7 @@
         <v>137124010</v>
       </c>
       <c r="B453" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -51036,7 +51036,7 @@
         <v>137291594</v>
       </c>
       <c r="B467" t="n">
-        <v>93481</v>
+        <v>93485</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>137144483</v>
       </c>
       <c r="B468" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>137144492</v>
       </c>
       <c r="B469" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>137291563</v>
       </c>
       <c r="B470" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>137291571</v>
       </c>
       <c r="B471" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -56069,7 +56069,7 @@
         <v>137016352</v>
       </c>
       <c r="B513" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>137016265</v>
       </c>
       <c r="B514" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>137511448</v>
       </c>
       <c r="B515" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -56398,7 +56398,7 @@
         <v>137511495</v>
       </c>
       <c r="B516" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -60633,7 +60633,7 @@
         <v>137290686</v>
       </c>
       <c r="B554" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>137291317</v>
       </c>
       <c r="B560" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -61730,7 +61730,7 @@
         <v>137291210</v>
       </c>
       <c r="B564" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -62158,7 +62158,7 @@
         <v>137290838</v>
       </c>
       <c r="B568" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -62264,7 +62264,7 @@
         <v>137290848</v>
       </c>
       <c r="B569" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -62370,7 +62370,7 @@
         <v>137290857</v>
       </c>
       <c r="B570" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -62476,7 +62476,7 @@
         <v>137291070</v>
       </c>
       <c r="B571" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -62582,7 +62582,7 @@
         <v>137291162</v>
       </c>
       <c r="B572" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -62688,7 +62688,7 @@
         <v>137291186</v>
       </c>
       <c r="B573" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -62794,7 +62794,7 @@
         <v>137291193</v>
       </c>
       <c r="B574" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         <v>137291218</v>
       </c>
       <c r="B575" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
         <v>137291263</v>
       </c>
       <c r="B576" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>137291298</v>
       </c>
       <c r="B577" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -63223,7 +63223,7 @@
         <v>137291402</v>
       </c>
       <c r="B578" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>137291412</v>
       </c>
       <c r="B579" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>137291421</v>
       </c>
       <c r="B580" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -65431,7 +65431,7 @@
         <v>137291426</v>
       </c>
       <c r="B598" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -65537,7 +65537,7 @@
         <v>137291430</v>
       </c>
       <c r="B599" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -65643,7 +65643,7 @@
         <v>137291534</v>
       </c>
       <c r="B600" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -65749,7 +65749,7 @@
         <v>137291554</v>
       </c>
       <c r="B601" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -67250,7 +67250,7 @@
         <v>137238726</v>
       </c>
       <c r="B615" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -67708,7 +67708,7 @@
         <v>137240254</v>
       </c>
       <c r="B619" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -68503,7 +68503,7 @@
         <v>137290579</v>
       </c>
       <c r="B626" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -69199,7 +69199,7 @@
         <v>137290591</v>
       </c>
       <c r="B632" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -69623,7 +69623,7 @@
         <v>137290729</v>
       </c>
       <c r="B636" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -69729,7 +69729,7 @@
         <v>137290756</v>
       </c>
       <c r="B637" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -69835,7 +69835,7 @@
         <v>137290815</v>
       </c>
       <c r="B638" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -72362,7 +72362,7 @@
         <v>137240024</v>
       </c>
       <c r="B661" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -72468,7 +72468,7 @@
         <v>137240039</v>
       </c>
       <c r="B662" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -72574,7 +72574,7 @@
         <v>137519610</v>
       </c>
       <c r="B663" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -73451,7 +73451,7 @@
         <v>137238841</v>
       </c>
       <c r="B671" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -73557,7 +73557,7 @@
         <v>137238858</v>
       </c>
       <c r="B672" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -73663,7 +73663,7 @@
         <v>137240141</v>
       </c>
       <c r="B673" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -74120,7 +74120,7 @@
         <v>137240203</v>
       </c>
       <c r="B677" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -74342,7 +74342,7 @@
         <v>137238811</v>
       </c>
       <c r="B679" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -76520,7 +76520,7 @@
         <v>137239472</v>
       </c>
       <c r="B699" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -76626,7 +76626,7 @@
         <v>137239964</v>
       </c>
       <c r="B700" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -76732,7 +76732,7 @@
         <v>137240074</v>
       </c>
       <c r="B701" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -77718,7 +77718,7 @@
         <v>137239535</v>
       </c>
       <c r="B710" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -77824,7 +77824,7 @@
         <v>137239564</v>
       </c>
       <c r="B711" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -77930,7 +77930,7 @@
         <v>137239989</v>
       </c>
       <c r="B712" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -78812,7 +78812,7 @@
         <v>137239483</v>
       </c>
       <c r="B720" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -78918,7 +78918,7 @@
         <v>137239495</v>
       </c>
       <c r="B721" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -79139,7 +79139,7 @@
         <v>128625864</v>
       </c>
       <c r="B723" t="n">
-        <v>93506</v>
+        <v>93510</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -79673,7 +79673,7 @@
         <v>137240122</v>
       </c>
       <c r="B728" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -79991,7 +79991,7 @@
         <v>137238959</v>
       </c>
       <c r="B731" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -80097,7 +80097,7 @@
         <v>137238973</v>
       </c>
       <c r="B732" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -80203,7 +80203,7 @@
         <v>137238992</v>
       </c>
       <c r="B733" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -80309,7 +80309,7 @@
         <v>137239263</v>
       </c>
       <c r="B734" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -80415,7 +80415,7 @@
         <v>137239323</v>
       </c>
       <c r="B735" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -80521,7 +80521,7 @@
         <v>137240084</v>
       </c>
       <c r="B736" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -81422,7 +81422,7 @@
         <v>137239011</v>
       </c>
       <c r="B744" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -81528,7 +81528,7 @@
         <v>137239194</v>
       </c>
       <c r="B745" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
